--- a/26spring list and group 260607.xlsx
+++ b/26spring list and group 260607.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lzz/github_teaching/emetrics26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8FD20A7-E6B0-0542-8A0B-B20C015E71A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA211B7-501A-F444-B4DF-E891F652E4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" firstSheet="3" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="计量进度" sheetId="5" r:id="rId1"/>
@@ -34,6 +34,9 @@
     <sheet name="第1周人力" sheetId="6" r:id="rId19"/>
     <sheet name="Sheet3" sheetId="7" r:id="rId20"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">统计分组!$A$1:$G$21</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -50,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3453" uniqueCount="1437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3453" uniqueCount="1438">
   <si>
     <t>华南农业大学学生课堂考勤表</t>
   </si>
@@ -8533,6 +8536,10 @@
       </rPr>
       <t>.pptx</t>
     </r>
+  </si>
+  <si>
+    <t>曾熙雯</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -8917,7 +8924,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9072,9 +9079,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -9109,6 +9113,42 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="19" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="22" fontId="20" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -9132,53 +9172,14 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="22" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="22" fontId="19" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="22" fontId="20" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11269,7 +11270,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="2" spans="2:2">
-      <c r="B2" s="62">
+      <c r="B2" s="61">
         <f>EXP(0.307)</f>
         <v>1.3593409680719806</v>
       </c>
@@ -11314,10 +11315,10 @@
       <c r="G1" s="31" t="s">
         <v>423</v>
       </c>
-      <c r="H1" s="57" t="s">
+      <c r="H1" s="56" t="s">
         <v>1197</v>
       </c>
-      <c r="I1" s="56" t="s">
+      <c r="I1" s="55" t="s">
         <v>1195</v>
       </c>
     </row>
@@ -11343,7 +11344,7 @@
       <c r="G2" s="35" t="s">
         <v>500</v>
       </c>
-      <c r="H2" s="57" t="s">
+      <c r="H2" s="56" t="s">
         <v>1217</v>
       </c>
       <c r="I2">
@@ -11375,7 +11376,7 @@
       <c r="G3" s="35" t="s">
         <v>504</v>
       </c>
-      <c r="H3" s="57" t="s">
+      <c r="H3" s="56" t="s">
         <v>1218</v>
       </c>
     </row>
@@ -11424,7 +11425,7 @@
       <c r="G5" s="35" t="s">
         <v>509</v>
       </c>
-      <c r="H5" s="56" t="s">
+      <c r="H5" s="55" t="s">
         <v>1219</v>
       </c>
     </row>
@@ -11448,7 +11449,7 @@
         <v>512</v>
       </c>
       <c r="G6" s="35"/>
-      <c r="H6" s="56" t="s">
+      <c r="H6" s="55" t="s">
         <v>1220</v>
       </c>
     </row>
@@ -11474,7 +11475,7 @@
       <c r="G7" s="35" t="s">
         <v>515</v>
       </c>
-      <c r="H7" s="56" t="s">
+      <c r="H7" s="55" t="s">
         <v>1225</v>
       </c>
     </row>
@@ -11498,7 +11499,7 @@
         <v>518</v>
       </c>
       <c r="G8" s="35"/>
-      <c r="H8" s="56" t="s">
+      <c r="H8" s="55" t="s">
         <v>1231</v>
       </c>
     </row>
@@ -11522,7 +11523,7 @@
         <v>521</v>
       </c>
       <c r="G9" s="35"/>
-      <c r="H9" s="56" t="s">
+      <c r="H9" s="55" t="s">
         <v>1221</v>
       </c>
     </row>
@@ -11548,7 +11549,7 @@
       <c r="G10" s="35" t="s">
         <v>525</v>
       </c>
-      <c r="H10" s="56" t="s">
+      <c r="H10" s="55" t="s">
         <v>1223</v>
       </c>
       <c r="I10">
@@ -11583,7 +11584,7 @@
       <c r="G11" s="35" t="s">
         <v>529</v>
       </c>
-      <c r="H11" s="56" t="s">
+      <c r="H11" s="55" t="s">
         <v>1224</v>
       </c>
     </row>
@@ -11609,7 +11610,7 @@
       <c r="G12" s="35" t="s">
         <v>532</v>
       </c>
-      <c r="H12" s="56" t="s">
+      <c r="H12" s="55" t="s">
         <v>1226</v>
       </c>
     </row>
@@ -11635,7 +11636,7 @@
       <c r="G13" s="35" t="s">
         <v>536</v>
       </c>
-      <c r="H13" s="56" t="s">
+      <c r="H13" s="55" t="s">
         <v>1227</v>
       </c>
     </row>
@@ -11661,7 +11662,7 @@
       <c r="G14" s="35" t="s">
         <v>540</v>
       </c>
-      <c r="H14" s="56" t="s">
+      <c r="H14" s="55" t="s">
         <v>1228</v>
       </c>
     </row>
@@ -11687,7 +11688,7 @@
       <c r="G15" s="35" t="s">
         <v>544</v>
       </c>
-      <c r="H15" s="56" t="s">
+      <c r="H15" s="55" t="s">
         <v>1229</v>
       </c>
     </row>
@@ -11746,7 +11747,7 @@
       <c r="G17" s="35" t="s">
         <v>548</v>
       </c>
-      <c r="H17" s="56" t="s">
+      <c r="H17" s="55" t="s">
         <v>1230</v>
       </c>
     </row>
@@ -11770,7 +11771,7 @@
         <v>551</v>
       </c>
       <c r="G18" s="42"/>
-      <c r="H18" s="56" t="s">
+      <c r="H18" s="55" t="s">
         <v>1232</v>
       </c>
       <c r="I18">
@@ -12726,91 +12727,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="76"/>
+      <c r="V1" s="76"/>
+      <c r="W1" s="76"/>
+      <c r="X1" s="76"/>
+      <c r="Y1" s="76"/>
     </row>
     <row r="2" spans="1:25" ht="21" customHeight="1">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="77" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="66"/>
-      <c r="T2" s="66"/>
-      <c r="U2" s="66"/>
-      <c r="V2" s="66"/>
-      <c r="W2" s="66"/>
-      <c r="X2" s="66"/>
-      <c r="Y2" s="66"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
+      <c r="W2" s="77"/>
+      <c r="X2" s="77"/>
+      <c r="Y2" s="77"/>
     </row>
     <row r="3" spans="1:25" ht="20" customHeight="1">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="78" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67"/>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="67"/>
-      <c r="X3" s="67"/>
-      <c r="Y3" s="67"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="78"/>
+      <c r="L3" s="78"/>
+      <c r="M3" s="78"/>
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="W3" s="78"/>
+      <c r="X3" s="78"/>
+      <c r="Y3" s="78"/>
     </row>
     <row r="4" spans="1:25" ht="28.5" customHeight="1">
       <c r="A4" s="6" t="s">
@@ -15366,91 +15367,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="68"/>
-      <c r="K1" s="68"/>
-      <c r="L1" s="68"/>
-      <c r="M1" s="68"/>
-      <c r="N1" s="68"/>
-      <c r="O1" s="68"/>
-      <c r="P1" s="68"/>
-      <c r="Q1" s="68"/>
-      <c r="R1" s="68"/>
-      <c r="S1" s="68"/>
-      <c r="T1" s="68"/>
-      <c r="U1" s="68"/>
-      <c r="V1" s="68"/>
-      <c r="W1" s="68"/>
-      <c r="X1" s="68"/>
-      <c r="Y1" s="68"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
+      <c r="V1" s="79"/>
+      <c r="W1" s="79"/>
+      <c r="X1" s="79"/>
+      <c r="Y1" s="79"/>
     </row>
     <row r="2" spans="1:25" ht="21" customHeight="1">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
-      <c r="U2" s="69"/>
-      <c r="V2" s="69"/>
-      <c r="W2" s="69"/>
-      <c r="X2" s="69"/>
-      <c r="Y2" s="69"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
+      <c r="V2" s="80"/>
+      <c r="W2" s="80"/>
+      <c r="X2" s="80"/>
+      <c r="Y2" s="80"/>
     </row>
     <row r="3" spans="1:25" ht="20" customHeight="1">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
-      <c r="M3" s="70"/>
-      <c r="N3" s="70"/>
-      <c r="O3" s="70"/>
-      <c r="P3" s="70"/>
-      <c r="Q3" s="70"/>
-      <c r="R3" s="70"/>
-      <c r="S3" s="70"/>
-      <c r="T3" s="70"/>
-      <c r="U3" s="70"/>
-      <c r="V3" s="70"/>
-      <c r="W3" s="70"/>
-      <c r="X3" s="70"/>
-      <c r="Y3" s="70"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="81"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="81"/>
+      <c r="S3" s="81"/>
+      <c r="T3" s="81"/>
+      <c r="U3" s="81"/>
+      <c r="V3" s="81"/>
+      <c r="W3" s="81"/>
+      <c r="X3" s="81"/>
+      <c r="Y3" s="81"/>
     </row>
     <row r="4" spans="1:25" ht="28.5" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -17725,91 +17726,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="27">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="76"/>
+      <c r="V1" s="76"/>
+      <c r="W1" s="76"/>
+      <c r="X1" s="76"/>
+      <c r="Y1" s="76"/>
     </row>
     <row r="2" spans="1:25" ht="21" customHeight="1">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="77" t="s">
         <v>346</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="66"/>
-      <c r="T2" s="66"/>
-      <c r="U2" s="66"/>
-      <c r="V2" s="66"/>
-      <c r="W2" s="66"/>
-      <c r="X2" s="66"/>
-      <c r="Y2" s="66"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
+      <c r="W2" s="77"/>
+      <c r="X2" s="77"/>
+      <c r="Y2" s="77"/>
     </row>
     <row r="3" spans="1:25" ht="20" customHeight="1">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="78" t="s">
         <v>347</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67"/>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="67"/>
-      <c r="X3" s="67"/>
-      <c r="Y3" s="67"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="78"/>
+      <c r="L3" s="78"/>
+      <c r="M3" s="78"/>
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="W3" s="78"/>
+      <c r="X3" s="78"/>
+      <c r="Y3" s="78"/>
     </row>
     <row r="4" spans="1:25" ht="28.5" customHeight="1">
       <c r="A4" s="6" t="s">
@@ -19139,91 +19140,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="27">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
-      <c r="I1" s="65"/>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="X1" s="65"/>
-      <c r="Y1" s="65"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
+      <c r="I1" s="76"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="76"/>
+      <c r="U1" s="76"/>
+      <c r="V1" s="76"/>
+      <c r="W1" s="76"/>
+      <c r="X1" s="76"/>
+      <c r="Y1" s="76"/>
     </row>
     <row r="2" spans="1:25" ht="21" customHeight="1">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="77" t="s">
         <v>279</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="66"/>
-      <c r="T2" s="66"/>
-      <c r="U2" s="66"/>
-      <c r="V2" s="66"/>
-      <c r="W2" s="66"/>
-      <c r="X2" s="66"/>
-      <c r="Y2" s="66"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="77"/>
+      <c r="U2" s="77"/>
+      <c r="V2" s="77"/>
+      <c r="W2" s="77"/>
+      <c r="X2" s="77"/>
+      <c r="Y2" s="77"/>
     </row>
     <row r="3" spans="1:25" ht="20" customHeight="1">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="78" t="s">
         <v>280</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67"/>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="67"/>
-      <c r="X3" s="67"/>
-      <c r="Y3" s="67"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="78"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="78"/>
+      <c r="G3" s="78"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="78"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="78"/>
+      <c r="L3" s="78"/>
+      <c r="M3" s="78"/>
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="W3" s="78"/>
+      <c r="X3" s="78"/>
+      <c r="Y3" s="78"/>
     </row>
     <row r="4" spans="1:25" ht="28.5" customHeight="1">
       <c r="A4" s="6" t="s">
@@ -20439,576 +20440,576 @@
   <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="6.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5" style="54" customWidth="1"/>
-    <col min="2" max="2" width="3.83203125" style="54" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="54" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" style="54" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.83203125" style="54" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5" style="54" customWidth="1"/>
-    <col min="7" max="7" width="12.5" style="54" customWidth="1"/>
-    <col min="8" max="8" width="83.33203125" style="54" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.5" style="54" customWidth="1"/>
-    <col min="10" max="10" width="8.1640625" style="54" customWidth="1"/>
-    <col min="11" max="16384" width="6.83203125" style="54"/>
+    <col min="1" max="2" width="6.5" style="53" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="53" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" style="53" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" style="53" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="53" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" style="53" customWidth="1"/>
+    <col min="8" max="8" width="83.33203125" style="53" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.5" style="53" customWidth="1"/>
+    <col min="10" max="10" width="8.1640625" style="53" customWidth="1"/>
+    <col min="11" max="16384" width="6.83203125" style="53"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="83" t="s">
         <v>1171</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="84" t="s">
         <v>421</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="84" t="s">
         <v>420</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="84" t="s">
         <v>422</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="84" t="s">
         <v>773</v>
       </c>
-      <c r="F1" s="52" t="s">
+      <c r="F1" s="84" t="s">
         <v>773</v>
       </c>
-      <c r="G1" s="52" t="s">
+      <c r="G1" s="84" t="s">
         <v>773</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="52" t="s">
         <v>1172</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="54">
+      <c r="A2" s="83">
         <v>1</v>
       </c>
-      <c r="B2" s="53">
+      <c r="B2" s="85">
         <v>4</v>
       </c>
-      <c r="C2" s="53" t="s">
-        <v>410</v>
-      </c>
-      <c r="D2" s="53" t="s">
+      <c r="C2" s="85" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D2" s="85" t="s">
         <v>774</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="85" t="s">
         <v>354</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="85" t="s">
         <v>349</v>
       </c>
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="85" t="s">
         <v>406</v>
       </c>
-      <c r="H2" s="53" t="s">
+      <c r="H2" s="52" t="s">
         <v>1187</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="54">
+      <c r="A3" s="83">
         <v>2</v>
       </c>
-      <c r="B3" s="53">
+      <c r="B3" s="85">
         <v>4</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="85" t="s">
         <v>356</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="85" t="s">
         <v>774</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="85" t="s">
         <v>412</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="85" t="s">
         <v>366</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="G3" s="85" t="s">
         <v>358</v>
       </c>
-      <c r="H3" s="53" t="s">
+      <c r="H3" s="52" t="s">
         <v>1186</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="54">
+      <c r="A4" s="83">
         <v>3</v>
       </c>
-      <c r="B4" s="53">
+      <c r="B4" s="85">
         <v>4</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="85" t="s">
         <v>374</v>
       </c>
-      <c r="D4" s="53" t="s">
+      <c r="D4" s="85" t="s">
         <v>774</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="85" t="s">
         <v>376</v>
       </c>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="85" t="s">
         <v>380</v>
       </c>
-      <c r="G4" s="53" t="s">
+      <c r="G4" s="85" t="s">
         <v>404</v>
       </c>
-      <c r="H4" s="53" t="s">
+      <c r="H4" s="52" t="s">
         <v>1188</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="54">
+      <c r="A5" s="83">
         <v>4</v>
       </c>
-      <c r="B5" s="53">
+      <c r="B5" s="85">
         <v>4</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="85" t="s">
         <v>386</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="85" t="s">
         <v>774</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="85" t="s">
         <v>352</v>
       </c>
-      <c r="F5" s="53" t="s">
+      <c r="F5" s="85" t="s">
         <v>402</v>
       </c>
-      <c r="G5" s="53" t="s">
+      <c r="G5" s="85" t="s">
         <v>400</v>
       </c>
-      <c r="H5" s="53" t="s">
+      <c r="H5" s="52" t="s">
         <v>1194</v>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="54">
+      <c r="A6" s="83">
         <v>5</v>
       </c>
-      <c r="B6" s="53">
+      <c r="B6" s="85">
         <v>4</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="85" t="s">
         <v>388</v>
       </c>
-      <c r="D6" s="53" t="s">
+      <c r="D6" s="85" t="s">
         <v>774</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="E6" s="85" t="s">
         <v>362</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="F6" s="85" t="s">
         <v>418</v>
       </c>
-      <c r="G6" s="53" t="s">
+      <c r="G6" s="85" t="s">
         <v>360</v>
       </c>
-      <c r="H6" s="53" t="s">
+      <c r="H6" s="52" t="s">
         <v>1189</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="54">
+      <c r="A7" s="83">
         <v>6</v>
       </c>
-      <c r="B7" s="53">
+      <c r="B7" s="85">
         <v>4</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="85" t="s">
         <v>390</v>
       </c>
-      <c r="D7" s="53" t="s">
+      <c r="D7" s="85" t="s">
         <v>774</v>
       </c>
-      <c r="E7" s="53" t="s">
+      <c r="E7" s="85" t="s">
         <v>370</v>
       </c>
-      <c r="F7" s="53" t="s">
+      <c r="F7" s="85" t="s">
         <v>394</v>
       </c>
-      <c r="G7" s="53" t="s">
+      <c r="G7" s="85" t="s">
         <v>382</v>
       </c>
-      <c r="H7" s="53" t="s">
+      <c r="H7" s="52" t="s">
         <v>1190</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="54">
+      <c r="A8" s="83">
         <v>7</v>
       </c>
-      <c r="B8" s="53">
+      <c r="B8" s="85">
         <v>4</v>
       </c>
-      <c r="C8" s="53" t="s">
+      <c r="C8" s="85" t="s">
         <v>398</v>
       </c>
-      <c r="D8" s="53" t="s">
+      <c r="D8" s="85" t="s">
         <v>774</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E8" s="85" t="s">
         <v>396</v>
       </c>
-      <c r="F8" s="53" t="s">
+      <c r="F8" s="85" t="s">
         <v>408</v>
       </c>
-      <c r="G8" s="53" t="s">
+      <c r="G8" s="85" t="s">
         <v>775</v>
       </c>
-      <c r="H8" s="53" t="s">
+      <c r="H8" s="52" t="s">
         <v>1191</v>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="54">
+      <c r="A9" s="83">
         <v>8</v>
       </c>
-      <c r="B9" s="53">
+      <c r="B9" s="85">
         <v>3</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="85" t="s">
         <v>392</v>
       </c>
-      <c r="D9" s="53" t="s">
+      <c r="D9" s="85" t="s">
         <v>774</v>
       </c>
-      <c r="E9" s="53" t="s">
+      <c r="E9" s="85" t="s">
         <v>414</v>
       </c>
-      <c r="F9" s="53" t="s">
+      <c r="F9" s="85" t="s">
         <v>416</v>
       </c>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53" t="s">
+      <c r="G9" s="85"/>
+      <c r="H9" s="52" t="s">
         <v>1192</v>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="54">
+      <c r="A10" s="83">
         <v>9</v>
       </c>
-      <c r="B10" s="53">
+      <c r="B10" s="85">
         <v>3</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="85" t="s">
         <v>781</v>
       </c>
-      <c r="D10" s="53" t="s">
+      <c r="D10" s="85" t="s">
         <v>777</v>
       </c>
-      <c r="E10" s="53" t="s">
+      <c r="E10" s="85" t="s">
         <v>780</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="85" t="s">
         <v>779</v>
       </c>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53" t="s">
+      <c r="G10" s="85"/>
+      <c r="H10" s="52" t="s">
         <v>1193</v>
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
+      <c r="A11" s="83"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="52"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="83" t="s">
         <v>1171</v>
       </c>
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="84" t="s">
         <v>421</v>
       </c>
-      <c r="C12" s="52" t="s">
+      <c r="C12" s="84" t="s">
         <v>420</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" s="84" t="s">
         <v>422</v>
       </c>
-      <c r="E12" s="52" t="s">
+      <c r="E12" s="84" t="s">
         <v>773</v>
       </c>
-      <c r="F12" s="52" t="s">
+      <c r="F12" s="84" t="s">
         <v>773</v>
       </c>
-      <c r="G12" s="52" t="s">
+      <c r="G12" s="84" t="s">
         <v>773</v>
       </c>
-      <c r="H12" s="53" t="s">
+      <c r="H12" s="52" t="s">
         <v>1172</v>
       </c>
-      <c r="I12" s="71" t="s">
+      <c r="I12" s="82" t="s">
         <v>1185</v>
       </c>
-      <c r="J12" s="71"/>
-      <c r="K12" s="71"/>
-      <c r="L12" s="71"/>
-      <c r="M12" s="71"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="82"/>
+      <c r="L12" s="82"/>
+      <c r="M12" s="82"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="54">
+      <c r="A13" s="83">
         <v>1</v>
       </c>
-      <c r="B13" s="53">
+      <c r="B13" s="85">
         <v>5</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="85" t="s">
         <v>287</v>
       </c>
-      <c r="D13" s="53" t="s">
+      <c r="D13" s="85" t="s">
         <v>776</v>
       </c>
-      <c r="E13" s="53" t="s">
+      <c r="E13" s="85" t="s">
         <v>297</v>
       </c>
-      <c r="F13" s="53" t="s">
+      <c r="F13" s="85" t="s">
         <v>315</v>
       </c>
-      <c r="G13" s="53" t="s">
+      <c r="G13" s="85" t="s">
         <v>1180</v>
       </c>
-      <c r="H13" s="53" t="s">
+      <c r="H13" s="52" t="s">
         <v>1182</v>
       </c>
-      <c r="I13" s="54">
+      <c r="I13" s="53">
         <v>4</v>
       </c>
-      <c r="J13" s="53" t="s">
+      <c r="J13" s="52" t="s">
         <v>287</v>
       </c>
-      <c r="K13" s="53" t="s">
+      <c r="K13" s="52" t="s">
         <v>297</v>
       </c>
-      <c r="L13" s="53" t="s">
+      <c r="L13" s="52" t="s">
         <v>315</v>
       </c>
-      <c r="M13" s="54" t="s">
+      <c r="M13" s="53" t="s">
         <v>1181</v>
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="54">
+      <c r="A14" s="83">
         <v>2</v>
       </c>
-      <c r="B14" s="53">
+      <c r="B14" s="85">
         <v>3</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="C14" s="85" t="s">
         <v>289</v>
       </c>
-      <c r="D14" s="53" t="s">
+      <c r="D14" s="85" t="s">
         <v>1170</v>
       </c>
-      <c r="E14" s="53" t="s">
+      <c r="E14" s="85" t="s">
         <v>309</v>
       </c>
-      <c r="F14" s="53" t="s">
+      <c r="F14" s="85" t="s">
         <v>305</v>
       </c>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53" t="s">
+      <c r="G14" s="85"/>
+      <c r="H14" s="52" t="s">
         <v>1184</v>
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="54">
+      <c r="A15" s="83">
         <v>3</v>
       </c>
-      <c r="B15" s="53">
+      <c r="B15" s="85">
         <v>4</v>
       </c>
-      <c r="C15" s="53" t="s">
+      <c r="C15" s="85" t="s">
         <v>299</v>
       </c>
-      <c r="D15" s="53" t="s">
+      <c r="D15" s="85" t="s">
         <v>776</v>
       </c>
-      <c r="E15" s="53" t="s">
+      <c r="E15" s="85" t="s">
         <v>333</v>
       </c>
-      <c r="F15" s="53" t="s">
+      <c r="F15" s="85" t="s">
         <v>337</v>
       </c>
-      <c r="G15" s="53" t="s">
+      <c r="G15" s="85" t="s">
         <v>303</v>
       </c>
-      <c r="H15" s="53" t="s">
+      <c r="H15" s="52" t="s">
         <v>1183</v>
       </c>
-      <c r="I15" s="54">
+      <c r="I15" s="53">
         <v>2</v>
       </c>
-      <c r="J15" s="53" t="s">
+      <c r="J15" s="52" t="s">
         <v>333</v>
       </c>
-      <c r="K15" s="53" t="s">
+      <c r="K15" s="52" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="54">
+      <c r="A16" s="83">
         <v>4</v>
       </c>
-      <c r="B16" s="53">
+      <c r="B16" s="85">
         <v>4</v>
       </c>
-      <c r="C16" s="53" t="s">
+      <c r="C16" s="85" t="s">
         <v>317</v>
       </c>
-      <c r="D16" s="53" t="s">
+      <c r="D16" s="85" t="s">
         <v>776</v>
       </c>
-      <c r="E16" s="53" t="s">
+      <c r="E16" s="85" t="s">
         <v>323</v>
       </c>
-      <c r="F16" s="53" t="s">
+      <c r="F16" s="85" t="s">
         <v>307</v>
       </c>
-      <c r="G16" s="53" t="s">
+      <c r="G16" s="85" t="s">
         <v>343</v>
       </c>
-      <c r="H16" s="53" t="s">
+      <c r="H16" s="52" t="s">
         <v>1174</v>
       </c>
-      <c r="J16" s="53"/>
-      <c r="K16" s="53"/>
+      <c r="J16" s="52"/>
+      <c r="K16" s="52"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="54">
+      <c r="A17" s="83">
         <v>5</v>
       </c>
-      <c r="B17" s="53">
+      <c r="B17" s="85">
         <v>4</v>
       </c>
-      <c r="C17" s="53" t="s">
+      <c r="C17" s="85" t="s">
         <v>329</v>
       </c>
-      <c r="D17" s="53" t="s">
+      <c r="D17" s="85" t="s">
         <v>776</v>
       </c>
-      <c r="E17" s="53" t="s">
+      <c r="E17" s="85" t="s">
         <v>327</v>
       </c>
-      <c r="F17" s="53" t="s">
+      <c r="F17" s="85" t="s">
         <v>295</v>
       </c>
-      <c r="G17" s="53" t="s">
+      <c r="G17" s="85" t="s">
         <v>345</v>
       </c>
-      <c r="H17" s="53" t="s">
+      <c r="H17" s="52" t="s">
         <v>1173</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="54">
+      <c r="A18" s="83">
         <v>6</v>
       </c>
-      <c r="B18" s="53">
+      <c r="B18" s="85">
         <v>4</v>
       </c>
-      <c r="C18" s="53" t="s">
+      <c r="C18" s="85" t="s">
         <v>339</v>
       </c>
-      <c r="D18" s="53" t="s">
+      <c r="D18" s="85" t="s">
         <v>776</v>
       </c>
-      <c r="E18" s="53" t="s">
+      <c r="E18" s="85" t="s">
         <v>301</v>
       </c>
-      <c r="F18" s="53" t="s">
+      <c r="F18" s="85" t="s">
         <v>285</v>
       </c>
-      <c r="G18" s="53" t="s">
+      <c r="G18" s="85" t="s">
         <v>313</v>
       </c>
-      <c r="H18" s="53" t="s">
+      <c r="H18" s="52" t="s">
         <v>1175</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="54">
+      <c r="A19" s="83">
         <v>7</v>
       </c>
-      <c r="B19" s="53">
+      <c r="B19" s="85">
         <v>4</v>
       </c>
-      <c r="C19" s="53" t="s">
+      <c r="C19" s="85" t="s">
         <v>331</v>
       </c>
-      <c r="D19" s="53" t="s">
+      <c r="D19" s="85" t="s">
         <v>776</v>
       </c>
-      <c r="E19" s="53" t="s">
+      <c r="E19" s="85" t="s">
         <v>293</v>
       </c>
-      <c r="F19" s="53" t="s">
+      <c r="F19" s="85" t="s">
         <v>311</v>
       </c>
-      <c r="G19" s="53" t="s">
+      <c r="G19" s="85" t="s">
         <v>1176</v>
       </c>
-      <c r="H19" s="53" t="s">
+      <c r="H19" s="52" t="s">
         <v>1177</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="54">
+      <c r="A20" s="83">
         <v>8</v>
       </c>
-      <c r="B20" s="53">
+      <c r="B20" s="85">
         <v>2</v>
       </c>
-      <c r="C20" s="53" t="s">
+      <c r="C20" s="85" t="s">
         <v>282</v>
       </c>
-      <c r="D20" s="53" t="s">
+      <c r="D20" s="85" t="s">
         <v>776</v>
       </c>
-      <c r="E20" s="53" t="s">
+      <c r="E20" s="85" t="s">
         <v>341</v>
       </c>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="53" t="s">
+      <c r="F20" s="85"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="52" t="s">
         <v>1178</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="54">
+      <c r="A21" s="83">
         <v>9</v>
       </c>
-      <c r="B21" s="53">
+      <c r="B21" s="85">
         <v>1</v>
       </c>
-      <c r="C21" s="53" t="s">
+      <c r="C21" s="85" t="s">
         <v>335</v>
       </c>
-      <c r="D21" s="53" t="s">
+      <c r="D21" s="85" t="s">
         <v>776</v>
       </c>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="54" t="s">
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="53" t="s">
         <v>1179</v>
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="B23" s="53">
+      <c r="B23" s="52">
         <f>SUM(B13:B21)</f>
         <v>31</v>
       </c>
-      <c r="C23" s="54" t="s">
+      <c r="C23" s="53" t="s">
         <v>782</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="17">
-      <c r="B32" s="55" t="s">
+      <c r="B32" s="54" t="s">
         <v>778</v>
       </c>
     </row>
@@ -24040,15 +24041,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="75" t="s">
         <v>1308</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
     </row>
     <row r="3" spans="1:7" ht="16">
       <c r="A3" s="35" t="s">
@@ -24877,7 +24878,7 @@
     <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="55.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="73" customWidth="1"/>
+    <col min="10" max="10" width="11" style="63" customWidth="1"/>
     <col min="11" max="11" width="78.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.83203125" customWidth="1"/>
   </cols>
@@ -24904,13 +24905,13 @@
       <c r="H1" s="35" t="s">
         <v>423</v>
       </c>
-      <c r="I1" s="72" t="s">
+      <c r="I1" s="56" t="s">
         <v>1309</v>
       </c>
-      <c r="J1" s="72" t="s">
+      <c r="J1" s="56" t="s">
         <v>1310</v>
       </c>
-      <c r="K1" s="72" t="s">
+      <c r="K1" s="56" t="s">
         <v>1327</v>
       </c>
     </row>
@@ -24936,7 +24937,7 @@
       <c r="H2" s="35" t="s">
         <v>500</v>
       </c>
-      <c r="K2" s="79" t="s">
+      <c r="K2" s="67" t="s">
         <v>1328</v>
       </c>
     </row>
@@ -24962,7 +24963,7 @@
       <c r="H3" s="35" t="s">
         <v>504</v>
       </c>
-      <c r="K3" s="79" t="s">
+      <c r="K3" s="67" t="s">
         <v>1329</v>
       </c>
     </row>
@@ -24982,7 +24983,7 @@
       <c r="F4" s="35"/>
       <c r="G4" s="35"/>
       <c r="H4" s="35"/>
-      <c r="K4" s="79" t="s">
+      <c r="K4" s="67" t="s">
         <v>1330</v>
       </c>
     </row>
@@ -25008,7 +25009,7 @@
       <c r="H5" s="35" t="s">
         <v>509</v>
       </c>
-      <c r="K5" s="79" t="s">
+      <c r="K5" s="67" t="s">
         <v>1331</v>
       </c>
     </row>
@@ -25032,7 +25033,7 @@
         <v>512</v>
       </c>
       <c r="H6" s="35"/>
-      <c r="K6" s="79" t="s">
+      <c r="K6" s="67" t="s">
         <v>1332</v>
       </c>
     </row>
@@ -25058,7 +25059,7 @@
       <c r="H7" s="35" t="s">
         <v>515</v>
       </c>
-      <c r="K7" s="79" t="s">
+      <c r="K7" s="67" t="s">
         <v>1333</v>
       </c>
     </row>
@@ -25082,7 +25083,7 @@
         <v>518</v>
       </c>
       <c r="H8" s="35"/>
-      <c r="K8" s="79" t="s">
+      <c r="K8" s="67" t="s">
         <v>1334</v>
       </c>
     </row>
@@ -25106,7 +25107,7 @@
         <v>521</v>
       </c>
       <c r="H9" s="35"/>
-      <c r="K9" s="79" t="s">
+      <c r="K9" s="67" t="s">
         <v>1335</v>
       </c>
     </row>
@@ -25132,7 +25133,7 @@
       <c r="H10" s="35" t="s">
         <v>525</v>
       </c>
-      <c r="K10" s="79" t="s">
+      <c r="K10" s="67" t="s">
         <v>1336</v>
       </c>
     </row>
@@ -25158,7 +25159,7 @@
       <c r="H11" s="35" t="s">
         <v>529</v>
       </c>
-      <c r="K11" s="79" t="s">
+      <c r="K11" s="67" t="s">
         <v>1337</v>
       </c>
     </row>
@@ -25184,7 +25185,7 @@
       <c r="H12" s="35" t="s">
         <v>532</v>
       </c>
-      <c r="K12" s="79" t="s">
+      <c r="K12" s="67" t="s">
         <v>1338</v>
       </c>
     </row>
@@ -25210,7 +25211,7 @@
       <c r="H13" s="35" t="s">
         <v>536</v>
       </c>
-      <c r="K13" s="79" t="s">
+      <c r="K13" s="67" t="s">
         <v>1339</v>
       </c>
     </row>
@@ -25236,7 +25237,7 @@
       <c r="H14" s="35" t="s">
         <v>540</v>
       </c>
-      <c r="K14" s="79" t="s">
+      <c r="K14" s="67" t="s">
         <v>1340</v>
       </c>
     </row>
@@ -25262,7 +25263,7 @@
       <c r="H15" s="35" t="s">
         <v>544</v>
       </c>
-      <c r="K15" s="79" t="s">
+      <c r="K15" s="67" t="s">
         <v>1341</v>
       </c>
     </row>
@@ -25309,7 +25310,7 @@
       <c r="H17" s="35" t="s">
         <v>548</v>
       </c>
-      <c r="K17" s="79" t="s">
+      <c r="K17" s="67" t="s">
         <v>1342</v>
       </c>
     </row>
@@ -25333,7 +25334,7 @@
         <v>551</v>
       </c>
       <c r="H18" s="35"/>
-      <c r="K18" s="79" t="s">
+      <c r="K18" s="67" t="s">
         <v>1343</v>
       </c>
     </row>
@@ -25382,13 +25383,13 @@
       <c r="H21" s="35" t="s">
         <v>434</v>
       </c>
-      <c r="I21" s="74">
+      <c r="I21" s="64">
         <v>46179.697916666664</v>
       </c>
-      <c r="J21" s="73">
+      <c r="J21" s="63">
         <v>1</v>
       </c>
-      <c r="K21" s="77" t="s">
+      <c r="K21" s="25" t="s">
         <v>1320</v>
       </c>
     </row>
@@ -25412,10 +25413,10 @@
         <v>437</v>
       </c>
       <c r="H22" s="35"/>
-      <c r="I22" s="74">
+      <c r="I22" s="64">
         <v>46179.854861111111</v>
       </c>
-      <c r="J22" s="73">
+      <c r="J22" s="63">
         <v>1</v>
       </c>
       <c r="K22" t="s">
@@ -25442,10 +25443,10 @@
         <v>440</v>
       </c>
       <c r="H23" s="35"/>
-      <c r="I23" s="75">
+      <c r="I23" s="65">
         <v>46179.505555555559</v>
       </c>
-      <c r="J23" s="73">
+      <c r="J23" s="63">
         <v>1</v>
       </c>
       <c r="K23" t="s">
@@ -25474,13 +25475,13 @@
       <c r="H24" s="35" t="s">
         <v>444</v>
       </c>
-      <c r="I24" s="75">
+      <c r="I24" s="65">
         <v>46180.630555555559</v>
       </c>
-      <c r="J24" s="73">
+      <c r="J24" s="63">
         <v>1</v>
       </c>
-      <c r="K24" s="78" t="s">
+      <c r="K24" s="55" t="s">
         <v>1313</v>
       </c>
     </row>
@@ -25506,10 +25507,10 @@
       <c r="H25" s="35" t="s">
         <v>448</v>
       </c>
-      <c r="I25" s="75">
+      <c r="I25" s="65">
         <v>46178.789583333331</v>
       </c>
-      <c r="J25" s="73">
+      <c r="J25" s="63">
         <v>0</v>
       </c>
       <c r="K25" t="s">
@@ -25538,7 +25539,7 @@
       <c r="H26" s="35" t="s">
         <v>454</v>
       </c>
-      <c r="I26" s="75"/>
+      <c r="I26" s="65"/>
     </row>
     <row r="27" spans="2:11" ht="16">
       <c r="B27" s="35">
@@ -25562,13 +25563,13 @@
       <c r="H27" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="I27" s="75">
+      <c r="I27" s="65">
         <v>46179.565972222219</v>
       </c>
-      <c r="J27" s="73">
+      <c r="J27" s="63">
         <v>1</v>
       </c>
-      <c r="K27" s="78" t="s">
+      <c r="K27" s="55" t="s">
         <v>1323</v>
       </c>
     </row>
@@ -25594,13 +25595,13 @@
       <c r="H28" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="I28" s="75">
+      <c r="I28" s="65">
         <v>46179.572916666664</v>
       </c>
-      <c r="J28" s="73">
+      <c r="J28" s="63">
         <v>1</v>
       </c>
-      <c r="K28" s="78" t="s">
+      <c r="K28" s="55" t="s">
         <v>1321</v>
       </c>
     </row>
@@ -25626,13 +25627,13 @@
       <c r="H29" s="35" t="s">
         <v>483</v>
       </c>
-      <c r="I29" s="74">
+      <c r="I29" s="64">
         <v>46180.776388888888</v>
       </c>
-      <c r="J29" s="73">
+      <c r="J29" s="63">
         <v>1</v>
       </c>
-      <c r="K29" s="77" t="s">
+      <c r="K29" s="25" t="s">
         <v>1315</v>
       </c>
     </row>
@@ -25658,13 +25659,13 @@
       <c r="H30" s="35" t="s">
         <v>467</v>
       </c>
-      <c r="I30" s="74">
+      <c r="I30" s="64">
         <v>46179.709027777775</v>
       </c>
-      <c r="J30" s="73">
+      <c r="J30" s="63">
         <v>1</v>
       </c>
-      <c r="K30" s="77" t="s">
+      <c r="K30" s="25" t="s">
         <v>1319</v>
       </c>
     </row>
@@ -25690,13 +25691,13 @@
       <c r="H31" s="35" t="s">
         <v>471</v>
       </c>
-      <c r="I31" s="74">
+      <c r="I31" s="64">
         <v>46179.709027777775</v>
       </c>
-      <c r="J31" s="73">
+      <c r="J31" s="63">
         <v>0</v>
       </c>
-      <c r="K31" s="77" t="s">
+      <c r="K31" s="25" t="s">
         <v>1311</v>
       </c>
     </row>
@@ -25722,10 +25723,10 @@
       <c r="H32" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="I32" s="76">
+      <c r="I32" s="66">
         <v>46180.762499999997</v>
       </c>
-      <c r="J32" s="73">
+      <c r="J32" s="63">
         <v>1</v>
       </c>
       <c r="K32" t="s">
@@ -25754,13 +25755,13 @@
       <c r="H33" s="35" t="s">
         <v>479</v>
       </c>
-      <c r="I33" s="74">
+      <c r="I33" s="64">
         <v>46180.79583333333</v>
       </c>
-      <c r="J33" s="73">
+      <c r="J33" s="63">
         <v>1</v>
       </c>
-      <c r="K33" s="77" t="s">
+      <c r="K33" s="25" t="s">
         <v>1316</v>
       </c>
     </row>
@@ -25786,10 +25787,10 @@
       <c r="H34" s="35" t="s">
         <v>772</v>
       </c>
-      <c r="I34" s="74">
+      <c r="I34" s="64">
         <v>46180.477777777778</v>
       </c>
-      <c r="J34" s="73">
+      <c r="J34" s="63">
         <v>1</v>
       </c>
       <c r="K34" t="s">
@@ -25818,13 +25819,13 @@
       <c r="H35" s="35" t="s">
         <v>487</v>
       </c>
-      <c r="I35" s="74">
+      <c r="I35" s="64">
         <v>46178.759722222225</v>
       </c>
-      <c r="J35" s="73">
+      <c r="J35" s="63">
         <v>1</v>
       </c>
-      <c r="K35" s="77" t="s">
+      <c r="K35" s="25" t="s">
         <v>1324</v>
       </c>
     </row>
@@ -25850,10 +25851,10 @@
       <c r="H36" s="35" t="s">
         <v>491</v>
       </c>
-      <c r="I36" s="75">
+      <c r="I36" s="65">
         <v>46178.802083333336</v>
       </c>
-      <c r="J36" s="73">
+      <c r="J36" s="63">
         <v>0</v>
       </c>
       <c r="K36" t="s">
@@ -25882,505 +25883,505 @@
       <c r="H37" s="35" t="s">
         <v>495</v>
       </c>
-      <c r="I37" s="75">
+      <c r="I37" s="65">
         <v>46180.630555555559</v>
       </c>
-      <c r="J37" s="73">
+      <c r="J37" s="63">
         <v>1</v>
       </c>
-      <c r="K37" s="78" t="s">
+      <c r="K37" s="55" t="s">
         <v>1312</v>
       </c>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="82" t="s">
+      <c r="A40" s="69" t="s">
         <v>1344</v>
       </c>
-      <c r="B40" s="80" t="s">
+      <c r="B40" s="68" t="s">
         <v>1345</v>
       </c>
-      <c r="C40" s="80" t="s">
+      <c r="C40" s="68" t="s">
         <v>1346</v>
       </c>
-      <c r="D40" s="80" t="s">
+      <c r="D40" s="68" t="s">
         <v>1347</v>
       </c>
-      <c r="E40" s="80" t="s">
+      <c r="E40" s="68" t="s">
         <v>1348</v>
       </c>
-      <c r="F40" s="80" t="s">
+      <c r="F40" s="68" t="s">
         <v>1349</v>
       </c>
-      <c r="G40" s="80" t="s">
+      <c r="G40" s="68" t="s">
         <v>1349</v>
       </c>
-      <c r="H40" s="80" t="s">
+      <c r="H40" s="68" t="s">
         <v>1349</v>
       </c>
-      <c r="I40" s="81" t="s">
+      <c r="I40" s="68" t="s">
         <v>1350</v>
       </c>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="83" t="s">
+      <c r="A41" s="71" t="s">
         <v>1351</v>
       </c>
-      <c r="B41" s="80">
+      <c r="B41" s="68">
         <v>1</v>
       </c>
-      <c r="C41" s="80" t="s">
+      <c r="C41" s="68" t="s">
         <v>1352</v>
       </c>
-      <c r="D41" s="80">
+      <c r="D41" s="68">
         <v>5</v>
       </c>
-      <c r="E41" s="80" t="s">
+      <c r="E41" s="68" t="s">
         <v>1353</v>
       </c>
-      <c r="F41" s="80" t="s">
+      <c r="F41" s="68" t="s">
         <v>1354</v>
       </c>
-      <c r="G41" s="80" t="s">
+      <c r="G41" s="68" t="s">
         <v>1355</v>
       </c>
-      <c r="H41" s="80" t="s">
+      <c r="H41" s="68" t="s">
         <v>1356</v>
       </c>
-      <c r="I41" s="81" t="s">
+      <c r="I41" s="68" t="s">
         <v>1357</v>
       </c>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="84"/>
-      <c r="B42" s="80">
+      <c r="A42" s="72"/>
+      <c r="B42" s="68">
         <v>2</v>
       </c>
-      <c r="C42" s="80" t="s">
+      <c r="C42" s="68" t="s">
         <v>1358</v>
       </c>
-      <c r="D42" s="80">
+      <c r="D42" s="68">
         <v>3</v>
       </c>
-      <c r="E42" s="80" t="s">
+      <c r="E42" s="68" t="s">
         <v>1353</v>
       </c>
-      <c r="F42" s="80" t="s">
+      <c r="F42" s="68" t="s">
         <v>1359</v>
       </c>
-      <c r="G42" s="80" t="s">
+      <c r="G42" s="68" t="s">
         <v>1360</v>
       </c>
-      <c r="H42" s="80"/>
-      <c r="I42" s="82" t="s">
+      <c r="H42" s="68"/>
+      <c r="I42" s="69" t="s">
         <v>1361</v>
       </c>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="84"/>
-      <c r="B43" s="80">
+      <c r="A43" s="72"/>
+      <c r="B43" s="68">
         <v>3</v>
       </c>
-      <c r="C43" s="80" t="s">
+      <c r="C43" s="68" t="s">
         <v>1362</v>
       </c>
-      <c r="D43" s="80">
+      <c r="D43" s="68">
         <v>3</v>
       </c>
-      <c r="E43" s="80" t="s">
+      <c r="E43" s="68" t="s">
         <v>1353</v>
       </c>
-      <c r="F43" s="80" t="s">
+      <c r="F43" s="68" t="s">
         <v>1363</v>
       </c>
-      <c r="G43" s="80" t="s">
+      <c r="G43" s="68" t="s">
         <v>1364</v>
       </c>
-      <c r="H43" s="80"/>
-      <c r="I43" s="82" t="s">
+      <c r="H43" s="68"/>
+      <c r="I43" s="69" t="s">
         <v>1365</v>
       </c>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="85"/>
-      <c r="B44" s="80">
+      <c r="A44" s="73"/>
+      <c r="B44" s="68">
         <v>7</v>
       </c>
-      <c r="C44" s="80" t="s">
+      <c r="C44" s="68" t="s">
         <v>1366</v>
       </c>
-      <c r="D44" s="80">
+      <c r="D44" s="68">
         <v>4</v>
       </c>
-      <c r="E44" s="80" t="s">
+      <c r="E44" s="68" t="s">
         <v>1353</v>
       </c>
-      <c r="F44" s="80" t="s">
+      <c r="F44" s="68" t="s">
         <v>1367</v>
       </c>
-      <c r="G44" s="80" t="s">
+      <c r="G44" s="68" t="s">
         <v>1368</v>
       </c>
-      <c r="H44" s="80" t="s">
+      <c r="H44" s="68" t="s">
         <v>1369</v>
       </c>
-      <c r="I44" s="81" t="s">
+      <c r="I44" s="68" t="s">
         <v>1370</v>
       </c>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="83" t="s">
+      <c r="A45" s="71" t="s">
         <v>1371</v>
       </c>
-      <c r="B45" s="80">
+      <c r="B45" s="68">
         <v>11</v>
       </c>
-      <c r="C45" s="80" t="s">
+      <c r="C45" s="68" t="s">
         <v>1372</v>
       </c>
-      <c r="D45" s="80">
+      <c r="D45" s="68">
         <v>4</v>
       </c>
-      <c r="E45" s="80" t="s">
+      <c r="E45" s="68" t="s">
         <v>1373</v>
       </c>
-      <c r="F45" s="80" t="s">
+      <c r="F45" s="68" t="s">
         <v>1374</v>
       </c>
-      <c r="G45" s="80" t="s">
+      <c r="G45" s="68" t="s">
         <v>1375</v>
       </c>
-      <c r="H45" s="80" t="s">
+      <c r="H45" s="68" t="s">
         <v>1376</v>
       </c>
-      <c r="I45" s="81" t="s">
+      <c r="I45" s="68" t="s">
         <v>1377</v>
       </c>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="84"/>
-      <c r="B46" s="80">
+      <c r="A46" s="72"/>
+      <c r="B46" s="68">
         <v>13</v>
       </c>
-      <c r="C46" s="80" t="s">
+      <c r="C46" s="68" t="s">
         <v>1378</v>
       </c>
-      <c r="D46" s="80">
+      <c r="D46" s="68">
         <v>5</v>
       </c>
-      <c r="E46" s="80" t="s">
+      <c r="E46" s="68" t="s">
         <v>1373</v>
       </c>
-      <c r="F46" s="80" t="s">
+      <c r="F46" s="68" t="s">
         <v>1379</v>
       </c>
-      <c r="G46" s="80" t="s">
+      <c r="G46" s="68" t="s">
         <v>1380</v>
       </c>
-      <c r="H46" s="80" t="s">
+      <c r="H46" s="68" t="s">
         <v>1381</v>
       </c>
-      <c r="I46" s="81" t="s">
+      <c r="I46" s="68" t="s">
         <v>1382</v>
       </c>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="84"/>
-      <c r="B47" s="80">
+      <c r="A47" s="72"/>
+      <c r="B47" s="68">
         <v>15</v>
       </c>
-      <c r="C47" s="80" t="s">
+      <c r="C47" s="68" t="s">
         <v>1383</v>
       </c>
-      <c r="D47" s="80">
+      <c r="D47" s="68">
         <v>4</v>
       </c>
-      <c r="E47" s="80" t="s">
+      <c r="E47" s="68" t="s">
         <v>1373</v>
       </c>
-      <c r="F47" s="80" t="s">
+      <c r="F47" s="68" t="s">
         <v>1384</v>
       </c>
-      <c r="G47" s="80" t="s">
+      <c r="G47" s="68" t="s">
         <v>1385</v>
       </c>
-      <c r="H47" s="80" t="s">
+      <c r="H47" s="68" t="s">
         <v>1386</v>
       </c>
-      <c r="I47" s="81" t="s">
+      <c r="I47" s="68" t="s">
         <v>1387</v>
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="85"/>
-      <c r="B48" s="80">
+      <c r="A48" s="73"/>
+      <c r="B48" s="68">
         <v>17</v>
       </c>
-      <c r="C48" s="80" t="s">
+      <c r="C48" s="68" t="s">
         <v>1388</v>
       </c>
-      <c r="D48" s="80">
+      <c r="D48" s="68">
         <v>4</v>
       </c>
-      <c r="E48" s="80" t="s">
+      <c r="E48" s="68" t="s">
         <v>1373</v>
       </c>
-      <c r="F48" s="80" t="s">
+      <c r="F48" s="68" t="s">
         <v>1389</v>
       </c>
-      <c r="G48" s="80" t="s">
+      <c r="G48" s="68" t="s">
         <v>1390</v>
       </c>
-      <c r="H48" s="80" t="s">
+      <c r="H48" s="68" t="s">
         <v>1391</v>
       </c>
-      <c r="I48" s="81" t="s">
+      <c r="I48" s="68" t="s">
         <v>1392</v>
       </c>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="82" t="s">
+      <c r="A51" s="69" t="s">
         <v>1393</v>
       </c>
-      <c r="B51" s="80" t="s">
+      <c r="B51" s="68" t="s">
         <v>1345</v>
       </c>
-      <c r="C51" s="80" t="s">
+      <c r="C51" s="68" t="s">
         <v>1346</v>
       </c>
-      <c r="D51" s="80" t="s">
+      <c r="D51" s="68" t="s">
         <v>1347</v>
       </c>
-      <c r="E51" s="80" t="s">
+      <c r="E51" s="68" t="s">
         <v>1348</v>
       </c>
-      <c r="F51" s="80" t="s">
+      <c r="F51" s="68" t="s">
         <v>1349</v>
       </c>
-      <c r="G51" s="80" t="s">
+      <c r="G51" s="68" t="s">
         <v>1349</v>
       </c>
-      <c r="H51" s="80" t="s">
+      <c r="H51" s="68" t="s">
         <v>1349</v>
       </c>
-      <c r="I51" s="81" t="s">
+      <c r="I51" s="68" t="s">
         <v>1350</v>
       </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="86" t="s">
+      <c r="A52" s="74" t="s">
         <v>1394</v>
       </c>
-      <c r="B52" s="80">
+      <c r="B52" s="68">
         <v>1</v>
       </c>
-      <c r="C52" s="80" t="s">
+      <c r="C52" s="68" t="s">
         <v>1395</v>
       </c>
-      <c r="D52" s="80">
+      <c r="D52" s="68">
         <v>4</v>
       </c>
-      <c r="E52" s="80" t="s">
+      <c r="E52" s="68" t="s">
         <v>1396</v>
       </c>
-      <c r="F52" s="80" t="s">
+      <c r="F52" s="68" t="s">
         <v>1397</v>
       </c>
-      <c r="G52" s="80" t="s">
+      <c r="G52" s="68" t="s">
         <v>1398</v>
       </c>
-      <c r="H52" s="80" t="s">
+      <c r="H52" s="68" t="s">
         <v>1399</v>
       </c>
-      <c r="I52" s="87" t="s">
+      <c r="I52" s="70" t="s">
         <v>1400</v>
       </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="86"/>
-      <c r="B53" s="80">
+      <c r="A53" s="74"/>
+      <c r="B53" s="68">
         <v>4</v>
       </c>
-      <c r="C53" s="80" t="s">
+      <c r="C53" s="68" t="s">
         <v>1401</v>
       </c>
-      <c r="D53" s="80">
+      <c r="D53" s="68">
         <v>5</v>
       </c>
-      <c r="E53" s="80" t="s">
+      <c r="E53" s="68" t="s">
         <v>1396</v>
       </c>
-      <c r="F53" s="80" t="s">
+      <c r="F53" s="68" t="s">
         <v>1402</v>
       </c>
-      <c r="G53" s="80" t="s">
+      <c r="G53" s="68" t="s">
         <v>1403</v>
       </c>
-      <c r="H53" s="80" t="s">
+      <c r="H53" s="68" t="s">
         <v>1404</v>
       </c>
-      <c r="I53" s="87" t="s">
+      <c r="I53" s="70" t="s">
         <v>1405</v>
       </c>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="86"/>
-      <c r="B54" s="80">
+      <c r="A54" s="74"/>
+      <c r="B54" s="68">
         <v>6</v>
       </c>
-      <c r="C54" s="80" t="s">
+      <c r="C54" s="68" t="s">
         <v>1406</v>
       </c>
-      <c r="D54" s="80">
+      <c r="D54" s="68">
         <v>5</v>
       </c>
-      <c r="E54" s="80" t="s">
+      <c r="E54" s="68" t="s">
         <v>1396</v>
       </c>
-      <c r="F54" s="80" t="s">
+      <c r="F54" s="68" t="s">
         <v>1407</v>
       </c>
-      <c r="G54" s="80" t="s">
+      <c r="G54" s="68" t="s">
         <v>1408</v>
       </c>
-      <c r="H54" s="80" t="s">
+      <c r="H54" s="68" t="s">
         <v>1409</v>
       </c>
-      <c r="I54" s="87" t="s">
+      <c r="I54" s="70" t="s">
         <v>1410</v>
       </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="86"/>
-      <c r="B55" s="80">
+      <c r="A55" s="74"/>
+      <c r="B55" s="68">
         <v>8</v>
       </c>
-      <c r="C55" s="80" t="s">
+      <c r="C55" s="68" t="s">
         <v>1411</v>
       </c>
-      <c r="D55" s="80">
+      <c r="D55" s="68">
         <v>3</v>
       </c>
-      <c r="E55" s="80" t="s">
+      <c r="E55" s="68" t="s">
         <v>1396</v>
       </c>
-      <c r="F55" s="80" t="s">
+      <c r="F55" s="68" t="s">
         <v>1412</v>
       </c>
-      <c r="G55" s="80" t="s">
+      <c r="G55" s="68" t="s">
         <v>1413</v>
       </c>
-      <c r="H55" s="80"/>
-      <c r="I55" s="87" t="s">
+      <c r="H55" s="68"/>
+      <c r="I55" s="70" t="s">
         <v>1414</v>
       </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="86" t="s">
+      <c r="A56" s="74" t="s">
         <v>1415</v>
       </c>
-      <c r="B56" s="80">
+      <c r="B56" s="68">
         <v>10</v>
       </c>
-      <c r="C56" s="80" t="s">
+      <c r="C56" s="68" t="s">
         <v>1416</v>
       </c>
-      <c r="D56" s="80">
+      <c r="D56" s="68">
         <v>4</v>
       </c>
-      <c r="E56" s="80" t="s">
+      <c r="E56" s="68" t="s">
         <v>1417</v>
       </c>
-      <c r="F56" s="80" t="s">
+      <c r="F56" s="68" t="s">
         <v>1418</v>
       </c>
-      <c r="G56" s="80" t="s">
+      <c r="G56" s="68" t="s">
         <v>1419</v>
       </c>
-      <c r="H56" s="80" t="s">
+      <c r="H56" s="68" t="s">
         <v>1420</v>
       </c>
-      <c r="I56" s="87" t="s">
+      <c r="I56" s="70" t="s">
         <v>1421</v>
       </c>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="86"/>
-      <c r="B57" s="80">
+      <c r="A57" s="74"/>
+      <c r="B57" s="68">
         <v>11</v>
       </c>
-      <c r="C57" s="80" t="s">
+      <c r="C57" s="68" t="s">
         <v>1422</v>
       </c>
-      <c r="D57" s="80">
+      <c r="D57" s="68">
         <v>4</v>
       </c>
-      <c r="E57" s="80" t="s">
+      <c r="E57" s="68" t="s">
         <v>1417</v>
       </c>
-      <c r="F57" s="80" t="s">
+      <c r="F57" s="68" t="s">
         <v>1423</v>
       </c>
-      <c r="G57" s="80" t="s">
+      <c r="G57" s="68" t="s">
         <v>1424</v>
       </c>
-      <c r="H57" s="80" t="s">
+      <c r="H57" s="68" t="s">
         <v>1425</v>
       </c>
-      <c r="I57" s="87" t="s">
+      <c r="I57" s="70" t="s">
         <v>1426</v>
       </c>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="86"/>
-      <c r="B58" s="80">
+      <c r="A58" s="74"/>
+      <c r="B58" s="68">
         <v>12</v>
       </c>
-      <c r="C58" s="80" t="s">
+      <c r="C58" s="68" t="s">
         <v>1427</v>
       </c>
-      <c r="D58" s="80">
+      <c r="D58" s="68">
         <v>4</v>
       </c>
-      <c r="E58" s="80" t="s">
+      <c r="E58" s="68" t="s">
         <v>1417</v>
       </c>
-      <c r="F58" s="80" t="s">
+      <c r="F58" s="68" t="s">
         <v>1428</v>
       </c>
-      <c r="G58" s="80" t="s">
+      <c r="G58" s="68" t="s">
         <v>1429</v>
       </c>
-      <c r="H58" s="80" t="s">
+      <c r="H58" s="68" t="s">
         <v>1430</v>
       </c>
-      <c r="I58" s="87" t="s">
+      <c r="I58" s="70" t="s">
         <v>1431</v>
       </c>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="86"/>
-      <c r="B59" s="80">
+      <c r="A59" s="74"/>
+      <c r="B59" s="68">
         <v>14</v>
       </c>
-      <c r="C59" s="80" t="s">
+      <c r="C59" s="68" t="s">
         <v>1432</v>
       </c>
-      <c r="D59" s="80">
+      <c r="D59" s="68">
         <v>4</v>
       </c>
-      <c r="E59" s="80" t="s">
+      <c r="E59" s="68" t="s">
         <v>1417</v>
       </c>
-      <c r="F59" s="80" t="s">
+      <c r="F59" s="68" t="s">
         <v>1433</v>
       </c>
-      <c r="G59" s="80" t="s">
+      <c r="G59" s="68" t="s">
         <v>1434</v>
       </c>
-      <c r="H59" s="80" t="s">
+      <c r="H59" s="68" t="s">
         <v>1435</v>
       </c>
-      <c r="I59" s="87" t="s">
+      <c r="I59" s="70" t="s">
         <v>1436</v>
       </c>
     </row>
@@ -26393,6 +26394,7 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -27812,22 +27814,22 @@
       <c r="H1" s="35" t="s">
         <v>423</v>
       </c>
-      <c r="I1" s="57" t="s">
+      <c r="I1" s="56" t="s">
         <v>1197</v>
       </c>
-      <c r="J1" s="56" t="s">
+      <c r="J1" s="55" t="s">
         <v>1185</v>
       </c>
-      <c r="K1" s="56" t="s">
+      <c r="K1" s="55" t="s">
         <v>1185</v>
       </c>
-      <c r="L1" s="56" t="s">
+      <c r="L1" s="55" t="s">
         <v>1185</v>
       </c>
-      <c r="M1" s="56" t="s">
+      <c r="M1" s="55" t="s">
         <v>1185</v>
       </c>
-      <c r="N1" s="56" t="s">
+      <c r="N1" s="55" t="s">
         <v>1185</v>
       </c>
     </row>
@@ -27856,7 +27858,7 @@
       <c r="H2" s="35" t="s">
         <v>434</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="56" t="s">
         <v>1196</v>
       </c>
       <c r="J2">
@@ -27892,7 +27894,7 @@
         <v>437</v>
       </c>
       <c r="H3" s="35"/>
-      <c r="I3" s="57" t="s">
+      <c r="I3" s="56" t="s">
         <v>1198</v>
       </c>
       <c r="J3">
@@ -27928,7 +27930,7 @@
         <v>440</v>
       </c>
       <c r="H4" s="35"/>
-      <c r="I4" s="57" t="s">
+      <c r="I4" s="56" t="s">
         <v>1199</v>
       </c>
     </row>
@@ -27957,7 +27959,7 @@
       <c r="H5" s="35" t="s">
         <v>444</v>
       </c>
-      <c r="I5" s="57" t="s">
+      <c r="I5" s="56" t="s">
         <v>1200</v>
       </c>
     </row>
@@ -27986,7 +27988,7 @@
       <c r="H6" s="35" t="s">
         <v>448</v>
       </c>
-      <c r="I6" s="57" t="s">
+      <c r="I6" s="56" t="s">
         <v>1201</v>
       </c>
     </row>
@@ -28056,7 +28058,7 @@
       <c r="H8" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="I8" s="56" t="s">
+      <c r="I8" s="55" t="s">
         <v>1202</v>
       </c>
     </row>
@@ -28085,7 +28087,7 @@
       <c r="H9" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="I9" s="56" t="s">
+      <c r="I9" s="55" t="s">
         <v>1203</v>
       </c>
     </row>
@@ -28114,7 +28116,7 @@
       <c r="H10" s="35" t="s">
         <v>483</v>
       </c>
-      <c r="I10" s="56" t="s">
+      <c r="I10" s="55" t="s">
         <v>1204</v>
       </c>
     </row>
@@ -28143,7 +28145,7 @@
       <c r="H11" s="35" t="s">
         <v>467</v>
       </c>
-      <c r="I11" s="56" t="s">
+      <c r="I11" s="55" t="s">
         <v>1205</v>
       </c>
     </row>
@@ -28172,7 +28174,7 @@
       <c r="H12" s="35" t="s">
         <v>471</v>
       </c>
-      <c r="I12" s="56" t="s">
+      <c r="I12" s="55" t="s">
         <v>1207</v>
       </c>
       <c r="J12">
@@ -28205,7 +28207,7 @@
       <c r="H13" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="I13" s="56" t="s">
+      <c r="I13" s="55" t="s">
         <v>1208</v>
       </c>
     </row>
@@ -28234,7 +28236,7 @@
       <c r="H14" s="35" t="s">
         <v>479</v>
       </c>
-      <c r="I14" s="56" t="s">
+      <c r="I14" s="55" t="s">
         <v>1209</v>
       </c>
     </row>
@@ -28261,7 +28263,7 @@
       <c r="H15" s="35" t="s">
         <v>772</v>
       </c>
-      <c r="I15" s="56" t="s">
+      <c r="I15" s="55" t="s">
         <v>1211</v>
       </c>
       <c r="J15">
@@ -28296,7 +28298,7 @@
       <c r="H16" s="35" t="s">
         <v>487</v>
       </c>
-      <c r="I16" s="56" t="s">
+      <c r="I16" s="55" t="s">
         <v>1213</v>
       </c>
       <c r="J16">
@@ -28331,7 +28333,7 @@
       <c r="H17" s="35" t="s">
         <v>491</v>
       </c>
-      <c r="I17" s="56" t="s">
+      <c r="I17" s="55" t="s">
         <v>1214</v>
       </c>
       <c r="J17">
@@ -28369,7 +28371,7 @@
       <c r="H18" s="35" t="s">
         <v>495</v>
       </c>
-      <c r="I18" s="56" t="s">
+      <c r="I18" s="55" t="s">
         <v>1215</v>
       </c>
     </row>
@@ -28418,16 +28420,16 @@
       <c r="H1" s="35" t="s">
         <v>423</v>
       </c>
-      <c r="I1" s="57" t="s">
+      <c r="I1" s="56" t="s">
         <v>1197</v>
       </c>
-      <c r="J1" s="57" t="s">
+      <c r="J1" s="56" t="s">
         <v>1249</v>
       </c>
-      <c r="K1" s="57" t="s">
+      <c r="K1" s="56" t="s">
         <v>1286</v>
       </c>
-      <c r="L1" s="57" t="s">
+      <c r="L1" s="56" t="s">
         <v>1251</v>
       </c>
       <c r="M1">
@@ -28459,12 +28461,12 @@
       <c r="H2" s="35" t="s">
         <v>454</v>
       </c>
-      <c r="I2" s="58"/>
-      <c r="J2" s="57" t="s">
+      <c r="I2" s="57"/>
+      <c r="J2" s="56" t="s">
         <v>1252</v>
       </c>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56" t="s">
+      <c r="K2" s="55"/>
+      <c r="L2" s="55" t="s">
         <v>1250</v>
       </c>
     </row>
@@ -28493,10 +28495,10 @@
       <c r="H3" s="35" t="s">
         <v>462</v>
       </c>
-      <c r="I3" s="57" t="s">
+      <c r="I3" s="56" t="s">
         <v>1203</v>
       </c>
-      <c r="J3" s="57" t="s">
+      <c r="J3" s="56" t="s">
         <v>1253</v>
       </c>
       <c r="K3" s="25"/>
@@ -28526,14 +28528,14 @@
       <c r="H4" s="35" t="s">
         <v>434</v>
       </c>
-      <c r="I4" s="57" t="s">
+      <c r="I4" s="56" t="s">
         <v>1196</v>
       </c>
-      <c r="J4" s="57" t="s">
+      <c r="J4" s="56" t="s">
         <v>1255</v>
       </c>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56" t="s">
+      <c r="K4" s="55"/>
+      <c r="L4" s="55" t="s">
         <v>1254</v>
       </c>
     </row>
@@ -28562,10 +28564,10 @@
       <c r="H5" s="35" t="s">
         <v>458</v>
       </c>
-      <c r="I5" s="57" t="s">
+      <c r="I5" s="56" t="s">
         <v>1202</v>
       </c>
-      <c r="J5" s="57" t="s">
+      <c r="J5" s="56" t="s">
         <v>1256</v>
       </c>
       <c r="K5" s="25"/>
@@ -28593,10 +28595,10 @@
         <v>440</v>
       </c>
       <c r="H6" s="35"/>
-      <c r="I6" s="57" t="s">
+      <c r="I6" s="56" t="s">
         <v>1199</v>
       </c>
-      <c r="J6" s="57" t="s">
+      <c r="J6" s="56" t="s">
         <v>1257</v>
       </c>
       <c r="K6" s="25"/>
@@ -28627,7 +28629,7 @@
       <c r="I7" s="25" t="s">
         <v>1198</v>
       </c>
-      <c r="J7" s="57" t="s">
+      <c r="J7" s="56" t="s">
         <v>1259</v>
       </c>
       <c r="K7" s="25"/>
@@ -28657,10 +28659,10 @@
       <c r="H8" s="35" t="s">
         <v>444</v>
       </c>
-      <c r="I8" s="56" t="s">
+      <c r="I8" s="55" t="s">
         <v>1200</v>
       </c>
-      <c r="J8" s="57" t="s">
+      <c r="J8" s="56" t="s">
         <v>1260</v>
       </c>
       <c r="K8" s="25"/>
@@ -28690,10 +28692,10 @@
       <c r="H9" s="35" t="s">
         <v>448</v>
       </c>
-      <c r="I9" s="56" t="s">
+      <c r="I9" s="55" t="s">
         <v>1201</v>
       </c>
-      <c r="J9" s="57" t="s">
+      <c r="J9" s="56" t="s">
         <v>1261</v>
       </c>
       <c r="K9" s="25"/>
@@ -28723,7 +28725,7 @@
       <c r="H10" s="35" t="s">
         <v>471</v>
       </c>
-      <c r="I10" s="56" t="s">
+      <c r="I10" s="55" t="s">
         <v>1207</v>
       </c>
       <c r="K10" s="25" t="s">
@@ -28758,7 +28760,7 @@
       <c r="H11" s="35" t="s">
         <v>479</v>
       </c>
-      <c r="I11" s="56" t="s">
+      <c r="I11" s="55" t="s">
         <v>1209</v>
       </c>
       <c r="K11" s="25" t="s">
@@ -28790,7 +28792,7 @@
       <c r="H12" s="35" t="s">
         <v>487</v>
       </c>
-      <c r="I12" s="56" t="s">
+      <c r="I12" s="55" t="s">
         <v>1213</v>
       </c>
       <c r="K12" s="25" t="s">
@@ -28828,7 +28830,7 @@
       <c r="H13" s="35" t="s">
         <v>483</v>
       </c>
-      <c r="I13" s="56" t="s">
+      <c r="I13" s="55" t="s">
         <v>1204</v>
       </c>
       <c r="K13" s="25" t="s">
@@ -28863,7 +28865,7 @@
       <c r="H14" s="35" t="s">
         <v>467</v>
       </c>
-      <c r="I14" s="56" t="s">
+      <c r="I14" s="55" t="s">
         <v>1205</v>
       </c>
       <c r="K14" s="25" t="s">
@@ -28895,7 +28897,7 @@
       <c r="H15" s="35" t="s">
         <v>491</v>
       </c>
-      <c r="I15" s="56" t="s">
+      <c r="I15" s="55" t="s">
         <v>1214</v>
       </c>
       <c r="K15" s="25" t="s">
@@ -28927,7 +28929,7 @@
       <c r="H16" s="35" t="s">
         <v>495</v>
       </c>
-      <c r="I16" s="56" t="s">
+      <c r="I16" s="55" t="s">
         <v>1215</v>
       </c>
       <c r="K16" s="25" t="s">
@@ -28957,7 +28959,7 @@
       <c r="H17" s="35" t="s">
         <v>475</v>
       </c>
-      <c r="I17" s="56" t="s">
+      <c r="I17" s="55" t="s">
         <v>1208</v>
       </c>
       <c r="K17" s="25" t="s">
@@ -28987,7 +28989,7 @@
       <c r="H18" s="35" t="s">
         <v>772</v>
       </c>
-      <c r="I18" s="56" t="s">
+      <c r="I18" s="55" t="s">
         <v>1211</v>
       </c>
       <c r="K18" s="25" t="s">
@@ -29047,31 +29049,31 @@
       <c r="H1" s="31" t="s">
         <v>423</v>
       </c>
-      <c r="I1" s="57" t="s">
+      <c r="I1" s="56" t="s">
         <v>1197</v>
       </c>
-      <c r="J1" s="56" t="s">
+      <c r="J1" s="55" t="s">
         <v>1185</v>
       </c>
-      <c r="K1" s="56" t="s">
+      <c r="K1" s="55" t="s">
         <v>1185</v>
       </c>
-      <c r="L1" s="56" t="s">
+      <c r="L1" s="55" t="s">
         <v>1185</v>
       </c>
-      <c r="M1" s="56" t="s">
+      <c r="M1" s="55" t="s">
         <v>1185</v>
       </c>
-      <c r="N1" s="56" t="s">
+      <c r="N1" s="55" t="s">
         <v>1299</v>
       </c>
-      <c r="O1" s="56" t="s">
+      <c r="O1" s="55" t="s">
         <v>1251</v>
       </c>
-      <c r="P1" s="56" t="s">
+      <c r="P1" s="55" t="s">
         <v>1251</v>
       </c>
-      <c r="Q1" s="56" t="s">
+      <c r="Q1" s="55" t="s">
         <v>1297</v>
       </c>
     </row>
@@ -29100,7 +29102,7 @@
       <c r="H2" s="35" t="s">
         <v>509</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="I2" s="56" t="s">
         <v>1219</v>
       </c>
       <c r="N2" t="s">
@@ -29130,7 +29132,7 @@
         <v>518</v>
       </c>
       <c r="H3" s="35"/>
-      <c r="I3" s="57" t="s">
+      <c r="I3" s="56" t="s">
         <v>1231</v>
       </c>
       <c r="N3" t="s">
@@ -29163,7 +29165,7 @@
       <c r="I4" s="25" t="s">
         <v>1221</v>
       </c>
-      <c r="K4" s="60"/>
+      <c r="K4" s="59"/>
       <c r="N4" t="s">
         <v>1274</v>
       </c>
@@ -29190,10 +29192,10 @@
       <c r="G5" s="35" t="s">
         <v>425</v>
       </c>
-      <c r="H5" s="61" t="s">
+      <c r="H5" s="60" t="s">
         <v>515</v>
       </c>
-      <c r="I5" s="56" t="s">
+      <c r="I5" s="55" t="s">
         <v>1225</v>
       </c>
       <c r="N5" t="s">
@@ -29225,7 +29227,7 @@
       <c r="H6" s="35" t="s">
         <v>500</v>
       </c>
-      <c r="I6" s="56" t="s">
+      <c r="I6" s="55" t="s">
         <v>1217</v>
       </c>
       <c r="J6">
@@ -29263,7 +29265,7 @@
       <c r="H7" s="35" t="s">
         <v>525</v>
       </c>
-      <c r="I7" s="56" t="s">
+      <c r="I7" s="55" t="s">
         <v>1223</v>
       </c>
       <c r="J7">
@@ -29302,7 +29304,7 @@
         <v>512</v>
       </c>
       <c r="H8" s="35"/>
-      <c r="I8" s="56" t="s">
+      <c r="I8" s="55" t="s">
         <v>1220</v>
       </c>
       <c r="N8" t="s">
@@ -29332,7 +29334,7 @@
       <c r="H9" s="35" t="s">
         <v>504</v>
       </c>
-      <c r="I9" s="56" t="s">
+      <c r="I9" s="55" t="s">
         <v>1218</v>
       </c>
       <c r="N9" t="s">
@@ -29362,7 +29364,7 @@
       <c r="F10" s="35"/>
       <c r="G10" s="35"/>
       <c r="H10" s="35"/>
-      <c r="I10" s="59" t="s">
+      <c r="I10" s="58" t="s">
         <v>1285</v>
       </c>
       <c r="J10">
@@ -29371,7 +29373,7 @@
       <c r="K10" s="35" t="s">
         <v>505</v>
       </c>
-      <c r="L10" s="60"/>
+      <c r="L10" s="59"/>
       <c r="N10" t="s">
         <v>1284</v>
       </c>
@@ -29401,7 +29403,7 @@
       <c r="H11" s="35" t="s">
         <v>544</v>
       </c>
-      <c r="I11" s="56" t="s">
+      <c r="I11" s="55" t="s">
         <v>1229</v>
       </c>
       <c r="N11" t="s">
@@ -29433,7 +29435,7 @@
       <c r="H12" s="35" t="s">
         <v>540</v>
       </c>
-      <c r="I12" s="56" t="s">
+      <c r="I12" s="55" t="s">
         <v>1296</v>
       </c>
       <c r="N12" t="s">
@@ -29468,7 +29470,7 @@
       <c r="H13" s="35" t="s">
         <v>529</v>
       </c>
-      <c r="I13" s="56" t="s">
+      <c r="I13" s="55" t="s">
         <v>1224</v>
       </c>
       <c r="N13" t="s">
@@ -29500,7 +29502,7 @@
       <c r="H14" s="35" t="s">
         <v>536</v>
       </c>
-      <c r="I14" s="56" t="s">
+      <c r="I14" s="55" t="s">
         <v>1227</v>
       </c>
       <c r="N14" t="s">
@@ -29532,7 +29534,7 @@
       <c r="H15" s="35" t="s">
         <v>532</v>
       </c>
-      <c r="I15" s="56" t="s">
+      <c r="I15" s="55" t="s">
         <v>1304</v>
       </c>
       <c r="N15" t="s">
@@ -29572,7 +29574,7 @@
       <c r="M16" s="35" t="s">
         <v>554</v>
       </c>
-      <c r="N16" s="63" t="s">
+      <c r="N16" s="62" t="s">
         <v>1195</v>
       </c>
     </row>
@@ -29599,7 +29601,7 @@
       <c r="H17" s="35" t="s">
         <v>548</v>
       </c>
-      <c r="I17" s="56" t="s">
+      <c r="I17" s="55" t="s">
         <v>1230</v>
       </c>
       <c r="N17" t="s">
@@ -29630,7 +29632,7 @@
         <v>551</v>
       </c>
       <c r="H18" s="42"/>
-      <c r="I18" s="56" t="s">
+      <c r="I18" s="55" t="s">
         <v>1232</v>
       </c>
       <c r="J18">

--- a/26spring list and group 260607.xlsx
+++ b/26spring list and group 260607.xlsx
@@ -8,34 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lzz/github_teaching/emetrics26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA211B7-501A-F444-B4DF-E891F652E4DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B64F99-82E1-5343-B0BD-7C8D71B83081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" firstSheet="3" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="计量进度" sheetId="5" r:id="rId1"/>
     <sheet name="publish" sheetId="12" r:id="rId2"/>
     <sheet name="group" sheetId="19" r:id="rId3"/>
     <sheet name="w15pre" sheetId="20" r:id="rId4"/>
-    <sheet name="W3选题" sheetId="10" r:id="rId5"/>
-    <sheet name="W7回归人资" sheetId="13" r:id="rId6"/>
-    <sheet name="W10人资" sheetId="15" r:id="rId7"/>
-    <sheet name="W10工管" sheetId="16" r:id="rId8"/>
-    <sheet name="Sheet4" sheetId="18" r:id="rId9"/>
-    <sheet name="Sheet2" sheetId="17" r:id="rId10"/>
-    <sheet name="W7回归工管" sheetId="14" r:id="rId11"/>
-    <sheet name="分组定稿" sheetId="11" r:id="rId12"/>
-    <sheet name="24人力" sheetId="2" r:id="rId13"/>
-    <sheet name="24工管" sheetId="1" r:id="rId14"/>
-    <sheet name="25会计2" sheetId="4" r:id="rId15"/>
-    <sheet name="25金融2" sheetId="3" r:id="rId16"/>
-    <sheet name="统计分组" sheetId="9" r:id="rId17"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId18"/>
-    <sheet name="第1周人力" sheetId="6" r:id="rId19"/>
-    <sheet name="Sheet3" sheetId="7" r:id="rId20"/>
+    <sheet name="Sheet5" sheetId="21" r:id="rId5"/>
+    <sheet name="W3选题" sheetId="10" r:id="rId6"/>
+    <sheet name="W7回归人资" sheetId="13" r:id="rId7"/>
+    <sheet name="W10人资" sheetId="15" r:id="rId8"/>
+    <sheet name="W10工管" sheetId="16" r:id="rId9"/>
+    <sheet name="Sheet4" sheetId="18" r:id="rId10"/>
+    <sheet name="Sheet2" sheetId="17" r:id="rId11"/>
+    <sheet name="W7回归工管" sheetId="14" r:id="rId12"/>
+    <sheet name="分组定稿" sheetId="11" r:id="rId13"/>
+    <sheet name="24人力" sheetId="2" r:id="rId14"/>
+    <sheet name="24工管" sheetId="1" r:id="rId15"/>
+    <sheet name="25会计2" sheetId="4" r:id="rId16"/>
+    <sheet name="25金融2" sheetId="3" r:id="rId17"/>
+    <sheet name="统计分组" sheetId="9" r:id="rId18"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId19"/>
+    <sheet name="第1周人力" sheetId="6" r:id="rId20"/>
+    <sheet name="Sheet3" sheetId="7" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">统计分组!$A$1:$G$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">统计分组!$A$1:$G$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3453" uniqueCount="1438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3455" uniqueCount="1439">
   <si>
     <t>华南农业大学学生课堂考勤表</t>
   </si>
@@ -5822,77 +5823,6 @@
         <rFont val="Helvetica Neue"/>
         <family val="2"/>
       </rPr>
-      <t>14</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>组祁栩琳</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>24</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>工商</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="PingFang SC"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>班瑞幸分布小组汇报</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>.pptx</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>第</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
       <t>16</t>
     </r>
     <r>
@@ -8540,6 +8470,14 @@
   <si>
     <t>曾熙雯</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>第14组祁栩琳24工商2班瑞幸分布小组汇报.pdf</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>文件名称</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -8924,7 +8862,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -9136,6 +9074,21 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -9147,9 +9100,6 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9169,17 +9119,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="22" fontId="19" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11265,6 +11215,65 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A84558C-36C6-4B03-911F-84558FD8E17A}">
+  <dimension ref="B1:D4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="4" width="13.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4">
+      <c r="B1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4">
+      <c r="B2">
+        <v>128</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="B3">
+        <v>256</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="B4">
+        <v>512</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB3C53C-44A1-4C7E-A7C1-EE52E2D3AB9D}">
   <dimension ref="B2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
@@ -11282,7 +11291,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DAD788D-949A-49FB-B3CF-88BF7FE61F68}">
   <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
@@ -11791,7 +11800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FFADBF3-7ED3-4149-8A52-E80B7FE0D6FF}">
   <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
@@ -12713,7 +12722,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB053F64-76DE-4B4F-BF9D-E00DD8E03B9E}">
   <dimension ref="A1:Y74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.83203125" defaultRowHeight="15"/>
@@ -12727,91 +12736,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="76"/>
-      <c r="Q1" s="76"/>
-      <c r="R1" s="76"/>
-      <c r="S1" s="76"/>
-      <c r="T1" s="76"/>
-      <c r="U1" s="76"/>
-      <c r="V1" s="76"/>
-      <c r="W1" s="76"/>
-      <c r="X1" s="76"/>
-      <c r="Y1" s="76"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="80"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+      <c r="S1" s="80"/>
+      <c r="T1" s="80"/>
+      <c r="U1" s="80"/>
+      <c r="V1" s="80"/>
+      <c r="W1" s="80"/>
+      <c r="X1" s="80"/>
+      <c r="Y1" s="80"/>
     </row>
     <row r="2" spans="1:25" ht="21" customHeight="1">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
-      <c r="W2" s="77"/>
-      <c r="X2" s="77"/>
-      <c r="Y2" s="77"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="81"/>
+      <c r="Y2" s="81"/>
     </row>
     <row r="3" spans="1:25" ht="20" customHeight="1">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="82" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="78"/>
-      <c r="R3" s="78"/>
-      <c r="S3" s="78"/>
-      <c r="T3" s="78"/>
-      <c r="U3" s="78"/>
-      <c r="V3" s="78"/>
-      <c r="W3" s="78"/>
-      <c r="X3" s="78"/>
-      <c r="Y3" s="78"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="82"/>
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
+      <c r="X3" s="82"/>
+      <c r="Y3" s="82"/>
     </row>
     <row r="4" spans="1:25" ht="28.5" customHeight="1">
       <c r="A4" s="6" t="s">
@@ -15352,7 +15361,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.83203125" defaultRowHeight="15"/>
@@ -15367,91 +15376,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="28.5" customHeight="1">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
-      <c r="O1" s="79"/>
-      <c r="P1" s="79"/>
-      <c r="Q1" s="79"/>
-      <c r="R1" s="79"/>
-      <c r="S1" s="79"/>
-      <c r="T1" s="79"/>
-      <c r="U1" s="79"/>
-      <c r="V1" s="79"/>
-      <c r="W1" s="79"/>
-      <c r="X1" s="79"/>
-      <c r="Y1" s="79"/>
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="83"/>
+      <c r="T1" s="83"/>
+      <c r="U1" s="83"/>
+      <c r="V1" s="83"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Y1" s="83"/>
     </row>
     <row r="2" spans="1:25" ht="21" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
-      <c r="P2" s="80"/>
-      <c r="Q2" s="80"/>
-      <c r="R2" s="80"/>
-      <c r="S2" s="80"/>
-      <c r="T2" s="80"/>
-      <c r="U2" s="80"/>
-      <c r="V2" s="80"/>
-      <c r="W2" s="80"/>
-      <c r="X2" s="80"/>
-      <c r="Y2" s="80"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+      <c r="R2" s="84"/>
+      <c r="S2" s="84"/>
+      <c r="T2" s="84"/>
+      <c r="U2" s="84"/>
+      <c r="V2" s="84"/>
+      <c r="W2" s="84"/>
+      <c r="X2" s="84"/>
+      <c r="Y2" s="84"/>
     </row>
     <row r="3" spans="1:25" ht="20" customHeight="1">
-      <c r="A3" s="81" t="s">
+      <c r="A3" s="85" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
-      <c r="O3" s="81"/>
-      <c r="P3" s="81"/>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="81"/>
-      <c r="S3" s="81"/>
-      <c r="T3" s="81"/>
-      <c r="U3" s="81"/>
-      <c r="V3" s="81"/>
-      <c r="W3" s="81"/>
-      <c r="X3" s="81"/>
-      <c r="Y3" s="81"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="85"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="85"/>
+      <c r="Q3" s="85"/>
+      <c r="R3" s="85"/>
+      <c r="S3" s="85"/>
+      <c r="T3" s="85"/>
+      <c r="U3" s="85"/>
+      <c r="V3" s="85"/>
+      <c r="W3" s="85"/>
+      <c r="X3" s="85"/>
+      <c r="Y3" s="85"/>
     </row>
     <row r="4" spans="1:25" ht="28.5" customHeight="1">
       <c r="A4" s="2" t="s">
@@ -17712,7 +17721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F4064D6-C1ED-1445-98CF-7FC1E20941E1}">
   <dimension ref="A1:Y39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.83203125" defaultRowHeight="15"/>
@@ -17726,91 +17735,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="27">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="76"/>
-      <c r="Q1" s="76"/>
-      <c r="R1" s="76"/>
-      <c r="S1" s="76"/>
-      <c r="T1" s="76"/>
-      <c r="U1" s="76"/>
-      <c r="V1" s="76"/>
-      <c r="W1" s="76"/>
-      <c r="X1" s="76"/>
-      <c r="Y1" s="76"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="80"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+      <c r="S1" s="80"/>
+      <c r="T1" s="80"/>
+      <c r="U1" s="80"/>
+      <c r="V1" s="80"/>
+      <c r="W1" s="80"/>
+      <c r="X1" s="80"/>
+      <c r="Y1" s="80"/>
     </row>
     <row r="2" spans="1:25" ht="21" customHeight="1">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="81" t="s">
         <v>346</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
-      <c r="W2" s="77"/>
-      <c r="X2" s="77"/>
-      <c r="Y2" s="77"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="81"/>
+      <c r="Y2" s="81"/>
     </row>
     <row r="3" spans="1:25" ht="20" customHeight="1">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="82" t="s">
         <v>347</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="78"/>
-      <c r="R3" s="78"/>
-      <c r="S3" s="78"/>
-      <c r="T3" s="78"/>
-      <c r="U3" s="78"/>
-      <c r="V3" s="78"/>
-      <c r="W3" s="78"/>
-      <c r="X3" s="78"/>
-      <c r="Y3" s="78"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="82"/>
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
+      <c r="X3" s="82"/>
+      <c r="Y3" s="82"/>
     </row>
     <row r="4" spans="1:25" ht="28.5" customHeight="1">
       <c r="A4" s="6" t="s">
@@ -19126,7 +19135,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{181AB12A-43F8-534C-ADCD-AFF80A001E10}">
   <dimension ref="A1:Y36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.83203125" defaultRowHeight="15"/>
@@ -19140,91 +19149,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="27">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="76"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="76"/>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="76"/>
-      <c r="P1" s="76"/>
-      <c r="Q1" s="76"/>
-      <c r="R1" s="76"/>
-      <c r="S1" s="76"/>
-      <c r="T1" s="76"/>
-      <c r="U1" s="76"/>
-      <c r="V1" s="76"/>
-      <c r="W1" s="76"/>
-      <c r="X1" s="76"/>
-      <c r="Y1" s="76"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="80"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+      <c r="S1" s="80"/>
+      <c r="T1" s="80"/>
+      <c r="U1" s="80"/>
+      <c r="V1" s="80"/>
+      <c r="W1" s="80"/>
+      <c r="X1" s="80"/>
+      <c r="Y1" s="80"/>
     </row>
     <row r="2" spans="1:25" ht="21" customHeight="1">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="81" t="s">
         <v>279</v>
       </c>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="77"/>
-      <c r="U2" s="77"/>
-      <c r="V2" s="77"/>
-      <c r="W2" s="77"/>
-      <c r="X2" s="77"/>
-      <c r="Y2" s="77"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="81"/>
+      <c r="Y2" s="81"/>
     </row>
     <row r="3" spans="1:25" ht="20" customHeight="1">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="82" t="s">
         <v>280</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
-      <c r="E3" s="78"/>
-      <c r="F3" s="78"/>
-      <c r="G3" s="78"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="78"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="78"/>
-      <c r="L3" s="78"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="78"/>
-      <c r="R3" s="78"/>
-      <c r="S3" s="78"/>
-      <c r="T3" s="78"/>
-      <c r="U3" s="78"/>
-      <c r="V3" s="78"/>
-      <c r="W3" s="78"/>
-      <c r="X3" s="78"/>
-      <c r="Y3" s="78"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="82"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="82"/>
+      <c r="Q3" s="82"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="82"/>
+      <c r="U3" s="82"/>
+      <c r="V3" s="82"/>
+      <c r="W3" s="82"/>
+      <c r="X3" s="82"/>
+      <c r="Y3" s="82"/>
     </row>
     <row r="4" spans="1:25" ht="28.5" customHeight="1">
       <c r="A4" s="6" t="s">
@@ -20435,7 +20444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59133ACC-6556-D947-8D3D-C348D695BBC1}">
   <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="6.83203125" defaultRowHeight="14"/>
@@ -20453,25 +20462,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="71" t="s">
         <v>1171</v>
       </c>
-      <c r="B1" s="84" t="s">
+      <c r="B1" s="72" t="s">
         <v>421</v>
       </c>
-      <c r="C1" s="84" t="s">
+      <c r="C1" s="72" t="s">
         <v>420</v>
       </c>
-      <c r="D1" s="84" t="s">
+      <c r="D1" s="72" t="s">
         <v>422</v>
       </c>
-      <c r="E1" s="84" t="s">
+      <c r="E1" s="72" t="s">
         <v>773</v>
       </c>
-      <c r="F1" s="84" t="s">
+      <c r="F1" s="72" t="s">
         <v>773</v>
       </c>
-      <c r="G1" s="84" t="s">
+      <c r="G1" s="72" t="s">
         <v>773</v>
       </c>
       <c r="H1" s="52" t="s">
@@ -20479,25 +20488,25 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="83">
+      <c r="A2" s="71">
         <v>1</v>
       </c>
-      <c r="B2" s="85">
+      <c r="B2" s="73">
         <v>4</v>
       </c>
-      <c r="C2" s="85" t="s">
-        <v>1437</v>
-      </c>
-      <c r="D2" s="85" t="s">
+      <c r="C2" s="73" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D2" s="73" t="s">
         <v>774</v>
       </c>
-      <c r="E2" s="85" t="s">
+      <c r="E2" s="73" t="s">
         <v>354</v>
       </c>
-      <c r="F2" s="85" t="s">
+      <c r="F2" s="73" t="s">
         <v>349</v>
       </c>
-      <c r="G2" s="85" t="s">
+      <c r="G2" s="73" t="s">
         <v>406</v>
       </c>
       <c r="H2" s="52" t="s">
@@ -20505,25 +20514,25 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="83">
+      <c r="A3" s="71">
         <v>2</v>
       </c>
-      <c r="B3" s="85">
+      <c r="B3" s="73">
         <v>4</v>
       </c>
-      <c r="C3" s="85" t="s">
+      <c r="C3" s="73" t="s">
         <v>356</v>
       </c>
-      <c r="D3" s="85" t="s">
+      <c r="D3" s="73" t="s">
         <v>774</v>
       </c>
-      <c r="E3" s="85" t="s">
+      <c r="E3" s="73" t="s">
         <v>412</v>
       </c>
-      <c r="F3" s="85" t="s">
+      <c r="F3" s="73" t="s">
         <v>366</v>
       </c>
-      <c r="G3" s="85" t="s">
+      <c r="G3" s="73" t="s">
         <v>358</v>
       </c>
       <c r="H3" s="52" t="s">
@@ -20531,25 +20540,25 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="83">
+      <c r="A4" s="71">
         <v>3</v>
       </c>
-      <c r="B4" s="85">
+      <c r="B4" s="73">
         <v>4</v>
       </c>
-      <c r="C4" s="85" t="s">
+      <c r="C4" s="73" t="s">
         <v>374</v>
       </c>
-      <c r="D4" s="85" t="s">
+      <c r="D4" s="73" t="s">
         <v>774</v>
       </c>
-      <c r="E4" s="85" t="s">
+      <c r="E4" s="73" t="s">
         <v>376</v>
       </c>
-      <c r="F4" s="85" t="s">
+      <c r="F4" s="73" t="s">
         <v>380</v>
       </c>
-      <c r="G4" s="85" t="s">
+      <c r="G4" s="73" t="s">
         <v>404</v>
       </c>
       <c r="H4" s="52" t="s">
@@ -20557,25 +20566,25 @@
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="83">
+      <c r="A5" s="71">
         <v>4</v>
       </c>
-      <c r="B5" s="85">
+      <c r="B5" s="73">
         <v>4</v>
       </c>
-      <c r="C5" s="85" t="s">
+      <c r="C5" s="73" t="s">
         <v>386</v>
       </c>
-      <c r="D5" s="85" t="s">
+      <c r="D5" s="73" t="s">
         <v>774</v>
       </c>
-      <c r="E5" s="85" t="s">
+      <c r="E5" s="73" t="s">
         <v>352</v>
       </c>
-      <c r="F5" s="85" t="s">
+      <c r="F5" s="73" t="s">
         <v>402</v>
       </c>
-      <c r="G5" s="85" t="s">
+      <c r="G5" s="73" t="s">
         <v>400</v>
       </c>
       <c r="H5" s="52" t="s">
@@ -20583,25 +20592,25 @@
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="83">
+      <c r="A6" s="71">
         <v>5</v>
       </c>
-      <c r="B6" s="85">
+      <c r="B6" s="73">
         <v>4</v>
       </c>
-      <c r="C6" s="85" t="s">
+      <c r="C6" s="73" t="s">
         <v>388</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="73" t="s">
         <v>774</v>
       </c>
-      <c r="E6" s="85" t="s">
+      <c r="E6" s="73" t="s">
         <v>362</v>
       </c>
-      <c r="F6" s="85" t="s">
+      <c r="F6" s="73" t="s">
         <v>418</v>
       </c>
-      <c r="G6" s="85" t="s">
+      <c r="G6" s="73" t="s">
         <v>360</v>
       </c>
       <c r="H6" s="52" t="s">
@@ -20609,25 +20618,25 @@
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="83">
+      <c r="A7" s="71">
         <v>6</v>
       </c>
-      <c r="B7" s="85">
+      <c r="B7" s="73">
         <v>4</v>
       </c>
-      <c r="C7" s="85" t="s">
+      <c r="C7" s="73" t="s">
         <v>390</v>
       </c>
-      <c r="D7" s="85" t="s">
+      <c r="D7" s="73" t="s">
         <v>774</v>
       </c>
-      <c r="E7" s="85" t="s">
+      <c r="E7" s="73" t="s">
         <v>370</v>
       </c>
-      <c r="F7" s="85" t="s">
+      <c r="F7" s="73" t="s">
         <v>394</v>
       </c>
-      <c r="G7" s="85" t="s">
+      <c r="G7" s="73" t="s">
         <v>382</v>
       </c>
       <c r="H7" s="52" t="s">
@@ -20635,25 +20644,25 @@
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="83">
+      <c r="A8" s="71">
         <v>7</v>
       </c>
-      <c r="B8" s="85">
+      <c r="B8" s="73">
         <v>4</v>
       </c>
-      <c r="C8" s="85" t="s">
+      <c r="C8" s="73" t="s">
         <v>398</v>
       </c>
-      <c r="D8" s="85" t="s">
+      <c r="D8" s="73" t="s">
         <v>774</v>
       </c>
-      <c r="E8" s="85" t="s">
+      <c r="E8" s="73" t="s">
         <v>396</v>
       </c>
-      <c r="F8" s="85" t="s">
+      <c r="F8" s="73" t="s">
         <v>408</v>
       </c>
-      <c r="G8" s="85" t="s">
+      <c r="G8" s="73" t="s">
         <v>775</v>
       </c>
       <c r="H8" s="52" t="s">
@@ -20661,116 +20670,116 @@
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="83">
+      <c r="A9" s="71">
         <v>8</v>
       </c>
-      <c r="B9" s="85">
+      <c r="B9" s="73">
         <v>3</v>
       </c>
-      <c r="C9" s="85" t="s">
+      <c r="C9" s="73" t="s">
         <v>392</v>
       </c>
-      <c r="D9" s="85" t="s">
+      <c r="D9" s="73" t="s">
         <v>774</v>
       </c>
-      <c r="E9" s="85" t="s">
+      <c r="E9" s="73" t="s">
         <v>414</v>
       </c>
-      <c r="F9" s="85" t="s">
+      <c r="F9" s="73" t="s">
         <v>416</v>
       </c>
-      <c r="G9" s="85"/>
+      <c r="G9" s="73"/>
       <c r="H9" s="52" t="s">
         <v>1192</v>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="83">
+      <c r="A10" s="71">
         <v>9</v>
       </c>
-      <c r="B10" s="85">
+      <c r="B10" s="73">
         <v>3</v>
       </c>
-      <c r="C10" s="85" t="s">
+      <c r="C10" s="73" t="s">
         <v>781</v>
       </c>
-      <c r="D10" s="85" t="s">
+      <c r="D10" s="73" t="s">
         <v>777</v>
       </c>
-      <c r="E10" s="85" t="s">
+      <c r="E10" s="73" t="s">
         <v>780</v>
       </c>
-      <c r="F10" s="85" t="s">
+      <c r="F10" s="73" t="s">
         <v>779</v>
       </c>
-      <c r="G10" s="85"/>
+      <c r="G10" s="73"/>
       <c r="H10" s="52" t="s">
         <v>1193</v>
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="83"/>
-      <c r="B11" s="85"/>
-      <c r="C11" s="85"/>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
+      <c r="A11" s="71"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
       <c r="H11" s="52"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="83" t="s">
+      <c r="A12" s="71" t="s">
         <v>1171</v>
       </c>
-      <c r="B12" s="84" t="s">
+      <c r="B12" s="72" t="s">
         <v>421</v>
       </c>
-      <c r="C12" s="84" t="s">
+      <c r="C12" s="72" t="s">
         <v>420</v>
       </c>
-      <c r="D12" s="84" t="s">
+      <c r="D12" s="72" t="s">
         <v>422</v>
       </c>
-      <c r="E12" s="84" t="s">
+      <c r="E12" s="72" t="s">
         <v>773</v>
       </c>
-      <c r="F12" s="84" t="s">
+      <c r="F12" s="72" t="s">
         <v>773</v>
       </c>
-      <c r="G12" s="84" t="s">
+      <c r="G12" s="72" t="s">
         <v>773</v>
       </c>
       <c r="H12" s="52" t="s">
         <v>1172</v>
       </c>
-      <c r="I12" s="82" t="s">
+      <c r="I12" s="74" t="s">
         <v>1185</v>
       </c>
-      <c r="J12" s="82"/>
-      <c r="K12" s="82"/>
-      <c r="L12" s="82"/>
-      <c r="M12" s="82"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="74"/>
+      <c r="L12" s="74"/>
+      <c r="M12" s="74"/>
     </row>
     <row r="13" spans="1:13">
-      <c r="A13" s="83">
+      <c r="A13" s="71">
         <v>1</v>
       </c>
-      <c r="B13" s="85">
+      <c r="B13" s="73">
         <v>5</v>
       </c>
-      <c r="C13" s="85" t="s">
+      <c r="C13" s="73" t="s">
         <v>287</v>
       </c>
-      <c r="D13" s="85" t="s">
+      <c r="D13" s="73" t="s">
         <v>776</v>
       </c>
-      <c r="E13" s="85" t="s">
+      <c r="E13" s="73" t="s">
         <v>297</v>
       </c>
-      <c r="F13" s="85" t="s">
+      <c r="F13" s="73" t="s">
         <v>315</v>
       </c>
-      <c r="G13" s="85" t="s">
+      <c r="G13" s="73" t="s">
         <v>1180</v>
       </c>
       <c r="H13" s="52" t="s">
@@ -20793,49 +20802,49 @@
       </c>
     </row>
     <row r="14" spans="1:13">
-      <c r="A14" s="83">
+      <c r="A14" s="71">
         <v>2</v>
       </c>
-      <c r="B14" s="85">
+      <c r="B14" s="73">
         <v>3</v>
       </c>
-      <c r="C14" s="85" t="s">
+      <c r="C14" s="73" t="s">
         <v>289</v>
       </c>
-      <c r="D14" s="85" t="s">
+      <c r="D14" s="73" t="s">
         <v>1170</v>
       </c>
-      <c r="E14" s="85" t="s">
+      <c r="E14" s="73" t="s">
         <v>309</v>
       </c>
-      <c r="F14" s="85" t="s">
+      <c r="F14" s="73" t="s">
         <v>305</v>
       </c>
-      <c r="G14" s="85"/>
+      <c r="G14" s="73"/>
       <c r="H14" s="52" t="s">
         <v>1184</v>
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="A15" s="83">
+      <c r="A15" s="71">
         <v>3</v>
       </c>
-      <c r="B15" s="85">
+      <c r="B15" s="73">
         <v>4</v>
       </c>
-      <c r="C15" s="85" t="s">
+      <c r="C15" s="73" t="s">
         <v>299</v>
       </c>
-      <c r="D15" s="85" t="s">
+      <c r="D15" s="73" t="s">
         <v>776</v>
       </c>
-      <c r="E15" s="85" t="s">
+      <c r="E15" s="73" t="s">
         <v>333</v>
       </c>
-      <c r="F15" s="85" t="s">
+      <c r="F15" s="73" t="s">
         <v>337</v>
       </c>
-      <c r="G15" s="85" t="s">
+      <c r="G15" s="73" t="s">
         <v>303</v>
       </c>
       <c r="H15" s="52" t="s">
@@ -20852,25 +20861,25 @@
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="A16" s="83">
+      <c r="A16" s="71">
         <v>4</v>
       </c>
-      <c r="B16" s="85">
+      <c r="B16" s="73">
         <v>4</v>
       </c>
-      <c r="C16" s="85" t="s">
+      <c r="C16" s="73" t="s">
         <v>317</v>
       </c>
-      <c r="D16" s="85" t="s">
+      <c r="D16" s="73" t="s">
         <v>776</v>
       </c>
-      <c r="E16" s="85" t="s">
+      <c r="E16" s="73" t="s">
         <v>323</v>
       </c>
-      <c r="F16" s="85" t="s">
+      <c r="F16" s="73" t="s">
         <v>307</v>
       </c>
-      <c r="G16" s="85" t="s">
+      <c r="G16" s="73" t="s">
         <v>343</v>
       </c>
       <c r="H16" s="52" t="s">
@@ -20880,25 +20889,25 @@
       <c r="K16" s="52"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="83">
+      <c r="A17" s="71">
         <v>5</v>
       </c>
-      <c r="B17" s="85">
+      <c r="B17" s="73">
         <v>4</v>
       </c>
-      <c r="C17" s="85" t="s">
+      <c r="C17" s="73" t="s">
         <v>329</v>
       </c>
-      <c r="D17" s="85" t="s">
+      <c r="D17" s="73" t="s">
         <v>776</v>
       </c>
-      <c r="E17" s="85" t="s">
+      <c r="E17" s="73" t="s">
         <v>327</v>
       </c>
-      <c r="F17" s="85" t="s">
+      <c r="F17" s="73" t="s">
         <v>295</v>
       </c>
-      <c r="G17" s="85" t="s">
+      <c r="G17" s="73" t="s">
         <v>345</v>
       </c>
       <c r="H17" s="52" t="s">
@@ -20906,25 +20915,25 @@
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="83">
+      <c r="A18" s="71">
         <v>6</v>
       </c>
-      <c r="B18" s="85">
+      <c r="B18" s="73">
         <v>4</v>
       </c>
-      <c r="C18" s="85" t="s">
+      <c r="C18" s="73" t="s">
         <v>339</v>
       </c>
-      <c r="D18" s="85" t="s">
+      <c r="D18" s="73" t="s">
         <v>776</v>
       </c>
-      <c r="E18" s="85" t="s">
+      <c r="E18" s="73" t="s">
         <v>301</v>
       </c>
-      <c r="F18" s="85" t="s">
+      <c r="F18" s="73" t="s">
         <v>285</v>
       </c>
-      <c r="G18" s="85" t="s">
+      <c r="G18" s="73" t="s">
         <v>313</v>
       </c>
       <c r="H18" s="52" t="s">
@@ -20932,25 +20941,25 @@
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="83">
+      <c r="A19" s="71">
         <v>7</v>
       </c>
-      <c r="B19" s="85">
+      <c r="B19" s="73">
         <v>4</v>
       </c>
-      <c r="C19" s="85" t="s">
+      <c r="C19" s="73" t="s">
         <v>331</v>
       </c>
-      <c r="D19" s="85" t="s">
+      <c r="D19" s="73" t="s">
         <v>776</v>
       </c>
-      <c r="E19" s="85" t="s">
+      <c r="E19" s="73" t="s">
         <v>293</v>
       </c>
-      <c r="F19" s="85" t="s">
+      <c r="F19" s="73" t="s">
         <v>311</v>
       </c>
-      <c r="G19" s="85" t="s">
+      <c r="G19" s="73" t="s">
         <v>1176</v>
       </c>
       <c r="H19" s="52" t="s">
@@ -20958,43 +20967,43 @@
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="83">
+      <c r="A20" s="71">
         <v>8</v>
       </c>
-      <c r="B20" s="85">
+      <c r="B20" s="73">
         <v>2</v>
       </c>
-      <c r="C20" s="85" t="s">
+      <c r="C20" s="73" t="s">
         <v>282</v>
       </c>
-      <c r="D20" s="85" t="s">
+      <c r="D20" s="73" t="s">
         <v>776</v>
       </c>
-      <c r="E20" s="85" t="s">
+      <c r="E20" s="73" t="s">
         <v>341</v>
       </c>
-      <c r="F20" s="85"/>
-      <c r="G20" s="85"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
       <c r="H20" s="52" t="s">
         <v>1178</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="83">
+      <c r="A21" s="71">
         <v>9</v>
       </c>
-      <c r="B21" s="85">
+      <c r="B21" s="73">
         <v>1</v>
       </c>
-      <c r="C21" s="85" t="s">
+      <c r="C21" s="73" t="s">
         <v>335</v>
       </c>
-      <c r="D21" s="85" t="s">
+      <c r="D21" s="73" t="s">
         <v>776</v>
       </c>
-      <c r="E21" s="85"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="85"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
       <c r="H21" s="53" t="s">
         <v>1179</v>
       </c>
@@ -21023,616 +21032,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7750C4B5-9B55-CC4B-9482-D16EB774F919}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
   <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90659A0F-F212-F044-BE56-4EC7AB740CAC}">
-  <dimension ref="A1:B74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
-  <cols>
-    <col min="1" max="1" width="25.1640625" style="17" customWidth="1"/>
-    <col min="2" max="2" width="19" style="17" customWidth="1"/>
-    <col min="3" max="16384" width="10.83203125" style="17"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="15" t="s">
-        <v>555</v>
-      </c>
-      <c r="B1" s="16"/>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="15" t="s">
-        <v>556</v>
-      </c>
-      <c r="B2" s="16"/>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="15" t="s">
-        <v>557</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="15" t="s">
-        <v>559</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="15" t="s">
-        <v>561</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="15" t="s">
-        <v>563</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="15" t="s">
-        <v>565</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="15" t="s">
-        <v>567</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="15" t="s">
-        <v>569</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="15" t="s">
-        <v>571</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="15" t="s">
-        <v>573</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="15" t="s">
-        <v>575</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="15" t="s">
-        <v>577</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="15" t="s">
-        <v>579</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="15" t="s">
-        <v>581</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="15" t="s">
-        <v>583</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="15" t="s">
-        <v>585</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="15" t="s">
-        <v>587</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="15" t="s">
-        <v>589</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="15" t="s">
-        <v>591</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="15" t="s">
-        <v>593</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="15" t="s">
-        <v>595</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="18" t="s">
-        <v>597</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="18" t="s">
-        <v>599</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="15" t="s">
-        <v>601</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="18" t="s">
-        <v>603</v>
-      </c>
-      <c r="B26" s="18" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="15" t="s">
-        <v>605</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="15" t="s">
-        <v>607</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="15" t="s">
-        <v>609</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="15" t="s">
-        <v>611</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="15" t="s">
-        <v>613</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="15" t="s">
-        <v>615</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="15" t="s">
-        <v>617</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="15" t="s">
-        <v>619</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="15" t="s">
-        <v>621</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="15" t="s">
-        <v>623</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="15" t="s">
-        <v>625</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="15" t="s">
-        <v>627</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="18" t="s">
-        <v>629</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="15" t="s">
-        <v>631</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="15" t="s">
-        <v>633</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="15" t="s">
-        <v>635</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="15" t="s">
-        <v>637</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="15" t="s">
-        <v>639</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="15" t="s">
-        <v>641</v>
-      </c>
-      <c r="B45" s="15" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="15" t="s">
-        <v>643</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="15" t="s">
-        <v>645</v>
-      </c>
-      <c r="B47" s="15" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="18" t="s">
-        <v>647</v>
-      </c>
-      <c r="B48" s="20">
-        <v>0.36736111111111114</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="15" t="s">
-        <v>648</v>
-      </c>
-      <c r="B49" s="19">
-        <v>0.52430555555555558</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="15" t="s">
-        <v>649</v>
-      </c>
-      <c r="B50" s="19">
-        <v>0.56458333333333333</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="15" t="s">
-        <v>650</v>
-      </c>
-      <c r="B51" s="19">
-        <v>0.57777777777777772</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="18">
-        <v>2</v>
-      </c>
-      <c r="B52" s="20">
-        <v>0.5805555555555556</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="15" t="s">
-        <v>651</v>
-      </c>
-      <c r="B53" s="19">
-        <v>0.63541666666666663</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="15" t="s">
-        <v>652</v>
-      </c>
-      <c r="B54" s="19">
-        <v>0.64166666666666672</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="15" t="s">
-        <v>653</v>
-      </c>
-      <c r="B55" s="19">
-        <v>0.65833333333333333</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="15" t="s">
-        <v>654</v>
-      </c>
-      <c r="B56" s="19">
-        <v>0.6694444444444444</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="15" t="s">
-        <v>655</v>
-      </c>
-      <c r="B57" s="19">
-        <v>0.76180555555555551</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="15" t="s">
-        <v>656</v>
-      </c>
-      <c r="B58" s="19">
-        <v>0.8125</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="15" t="s">
-        <v>657</v>
-      </c>
-      <c r="B59" s="19">
-        <v>0.83125000000000004</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" s="15" t="s">
-        <v>658</v>
-      </c>
-      <c r="B60" s="19">
-        <v>0.83125000000000004</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" s="15" t="s">
-        <v>659</v>
-      </c>
-      <c r="B61" s="19">
-        <v>0.83125000000000004</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="15" t="s">
-        <v>660</v>
-      </c>
-      <c r="B62" s="15" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" s="15" t="s">
-        <v>662</v>
-      </c>
-      <c r="B63" s="15" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" s="15" t="s">
-        <v>663</v>
-      </c>
-      <c r="B64" s="15" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" s="15" t="s">
-        <v>664</v>
-      </c>
-      <c r="B65" s="15" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" s="15" t="s">
-        <v>665</v>
-      </c>
-      <c r="B66" s="15" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" s="15" t="s">
-        <v>666</v>
-      </c>
-      <c r="B67" s="15" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" s="18" t="s">
-        <v>667</v>
-      </c>
-      <c r="B68" s="18" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" s="18" t="s">
-        <v>668</v>
-      </c>
-      <c r="B69" s="18" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" s="15" t="s">
-        <v>669</v>
-      </c>
-      <c r="B70" s="15" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" s="15" t="s">
-        <v>670</v>
-      </c>
-      <c r="B71" s="15" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" s="15" t="s">
-        <v>671</v>
-      </c>
-      <c r="B72" s="15" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" s="15" t="s">
-        <v>672</v>
-      </c>
-      <c r="B73" s="15" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" s="15" t="s">
-        <v>673</v>
-      </c>
-      <c r="B74" s="15" t="s">
-        <v>661</v>
-      </c>
-    </row>
-  </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -23467,6 +22871,611 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90659A0F-F212-F044-BE56-4EC7AB740CAC}">
+  <dimension ref="A1:B74"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="25.1640625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="19" style="17" customWidth="1"/>
+    <col min="3" max="16384" width="10.83203125" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="15" t="s">
+        <v>555</v>
+      </c>
+      <c r="B1" s="16"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="15" t="s">
+        <v>556</v>
+      </c>
+      <c r="B2" s="16"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="15" t="s">
+        <v>557</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="15" t="s">
+        <v>559</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="15" t="s">
+        <v>561</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="15" t="s">
+        <v>563</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="15" t="s">
+        <v>567</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="15" t="s">
+        <v>569</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="15" t="s">
+        <v>571</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="15" t="s">
+        <v>573</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="15" t="s">
+        <v>575</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="15" t="s">
+        <v>577</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="15" t="s">
+        <v>579</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="15" t="s">
+        <v>581</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="15" t="s">
+        <v>583</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="15" t="s">
+        <v>585</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="15" t="s">
+        <v>587</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="15" t="s">
+        <v>589</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="15" t="s">
+        <v>591</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="15" t="s">
+        <v>593</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="15" t="s">
+        <v>595</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="18" t="s">
+        <v>597</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="18" t="s">
+        <v>599</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="15" t="s">
+        <v>601</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="18" t="s">
+        <v>603</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="15" t="s">
+        <v>605</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="15" t="s">
+        <v>607</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="15" t="s">
+        <v>609</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="15" t="s">
+        <v>611</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="15" t="s">
+        <v>613</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="15" t="s">
+        <v>615</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="15" t="s">
+        <v>617</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="15" t="s">
+        <v>619</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="15" t="s">
+        <v>621</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="15" t="s">
+        <v>623</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="15" t="s">
+        <v>625</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="15" t="s">
+        <v>627</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="18" t="s">
+        <v>629</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="15" t="s">
+        <v>631</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="15" t="s">
+        <v>635</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="15" t="s">
+        <v>637</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="15" t="s">
+        <v>639</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="15" t="s">
+        <v>641</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="15" t="s">
+        <v>643</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="15" t="s">
+        <v>645</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="18" t="s">
+        <v>647</v>
+      </c>
+      <c r="B48" s="20">
+        <v>0.36736111111111114</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="B49" s="19">
+        <v>0.52430555555555558</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="15" t="s">
+        <v>649</v>
+      </c>
+      <c r="B50" s="19">
+        <v>0.56458333333333333</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="15" t="s">
+        <v>650</v>
+      </c>
+      <c r="B51" s="19">
+        <v>0.57777777777777772</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="18">
+        <v>2</v>
+      </c>
+      <c r="B52" s="20">
+        <v>0.5805555555555556</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="15" t="s">
+        <v>651</v>
+      </c>
+      <c r="B53" s="19">
+        <v>0.63541666666666663</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="15" t="s">
+        <v>652</v>
+      </c>
+      <c r="B54" s="19">
+        <v>0.64166666666666672</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="B55" s="19">
+        <v>0.65833333333333333</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="15" t="s">
+        <v>654</v>
+      </c>
+      <c r="B56" s="19">
+        <v>0.6694444444444444</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="15" t="s">
+        <v>655</v>
+      </c>
+      <c r="B57" s="19">
+        <v>0.76180555555555551</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="15" t="s">
+        <v>656</v>
+      </c>
+      <c r="B58" s="19">
+        <v>0.8125</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="15" t="s">
+        <v>657</v>
+      </c>
+      <c r="B59" s="19">
+        <v>0.83125000000000004</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="15" t="s">
+        <v>658</v>
+      </c>
+      <c r="B60" s="19">
+        <v>0.83125000000000004</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="15" t="s">
+        <v>659</v>
+      </c>
+      <c r="B61" s="19">
+        <v>0.83125000000000004</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="15" t="s">
+        <v>660</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="15" t="s">
+        <v>662</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="15" t="s">
+        <v>663</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="15" t="s">
+        <v>664</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="15" t="s">
+        <v>665</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="15" t="s">
+        <v>666</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="18" t="s">
+        <v>667</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="18" t="s">
+        <v>668</v>
+      </c>
+      <c r="B69" s="18" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="15" t="s">
+        <v>670</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="15" t="s">
+        <v>671</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="15" t="s">
+        <v>672</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="15" t="s">
+        <v>673</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>661</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A84614CC-9406-C446-8F8F-B5A5631DB511}">
   <dimension ref="A1:B69"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
@@ -24877,8 +24886,8 @@
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
     <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="55.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="63" customWidth="1"/>
+    <col min="9" max="9" width="18.1640625" customWidth="1"/>
+    <col min="10" max="10" width="11" style="63" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="78.6640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.83203125" customWidth="1"/>
   </cols>
@@ -25264,29 +25273,32 @@
         <v>544</v>
       </c>
       <c r="K15" s="67" t="s">
-        <v>1341</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="16" spans="2:11" ht="16">
-      <c r="B16" s="35">
+      <c r="B16" s="86">
         <v>15</v>
       </c>
-      <c r="C16" s="35" t="s">
+      <c r="C16" s="86" t="s">
         <v>552</v>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="86">
         <v>3</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="86" t="s">
         <v>427</v>
       </c>
-      <c r="F16" s="35" t="s">
+      <c r="F16" s="86" t="s">
         <v>553</v>
       </c>
-      <c r="G16" s="35" t="s">
+      <c r="G16" s="86" t="s">
         <v>554</v>
       </c>
-      <c r="H16" s="35"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="87"/>
+      <c r="J16" s="88"/>
+      <c r="K16" s="87"/>
     </row>
     <row r="17" spans="2:11" ht="16">
       <c r="B17" s="35">
@@ -25311,7 +25323,7 @@
         <v>548</v>
       </c>
       <c r="K17" s="67" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="16">
@@ -25335,7 +25347,7 @@
       </c>
       <c r="H18" s="35"/>
       <c r="K18" s="67" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="16">
@@ -25360,6 +25372,12 @@
       <c r="H20" s="35" t="s">
         <v>423</v>
       </c>
+      <c r="I20" s="56" t="s">
+        <v>1309</v>
+      </c>
+      <c r="K20" s="67" t="s">
+        <v>1438</v>
+      </c>
     </row>
     <row r="21" spans="2:11" ht="16">
       <c r="B21" s="35">
@@ -25518,28 +25536,30 @@
       </c>
     </row>
     <row r="26" spans="2:11" ht="16">
-      <c r="B26" s="35">
+      <c r="B26" s="86">
         <v>6</v>
       </c>
-      <c r="C26" s="35" t="s">
+      <c r="C26" s="86" t="s">
         <v>451</v>
       </c>
-      <c r="D26" s="35">
+      <c r="D26" s="86">
         <v>4</v>
       </c>
-      <c r="E26" s="35" t="s">
+      <c r="E26" s="86" t="s">
         <v>431</v>
       </c>
-      <c r="F26" s="35" t="s">
+      <c r="F26" s="86" t="s">
         <v>452</v>
       </c>
-      <c r="G26" s="35" t="s">
+      <c r="G26" s="86" t="s">
         <v>453</v>
       </c>
-      <c r="H26" s="35" t="s">
+      <c r="H26" s="86" t="s">
         <v>454</v>
       </c>
-      <c r="I26" s="65"/>
+      <c r="I26" s="89"/>
+      <c r="J26" s="88"/>
+      <c r="K26" s="87"/>
     </row>
     <row r="27" spans="2:11" ht="16">
       <c r="B27" s="35">
@@ -25895,494 +25915,494 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="69" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B40" s="68" t="s">
         <v>1344</v>
       </c>
-      <c r="B40" s="68" t="s">
+      <c r="C40" s="68" t="s">
         <v>1345</v>
       </c>
-      <c r="C40" s="68" t="s">
+      <c r="D40" s="68" t="s">
         <v>1346</v>
       </c>
-      <c r="D40" s="68" t="s">
+      <c r="E40" s="68" t="s">
         <v>1347</v>
       </c>
-      <c r="E40" s="68" t="s">
+      <c r="F40" s="68" t="s">
         <v>1348</v>
       </c>
-      <c r="F40" s="68" t="s">
+      <c r="G40" s="68" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H40" s="68" t="s">
+        <v>1348</v>
+      </c>
+      <c r="I40" s="68" t="s">
         <v>1349</v>
       </c>
-      <c r="G40" s="68" t="s">
-        <v>1349</v>
-      </c>
-      <c r="H40" s="68" t="s">
-        <v>1349</v>
-      </c>
-      <c r="I40" s="68" t="s">
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="76" t="s">
         <v>1350</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="71" t="s">
-        <v>1351</v>
       </c>
       <c r="B41" s="68">
         <v>1</v>
       </c>
       <c r="C41" s="68" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D41" s="68">
         <v>5</v>
       </c>
       <c r="E41" s="68" t="s">
+        <v>1352</v>
+      </c>
+      <c r="F41" s="68" t="s">
         <v>1353</v>
       </c>
-      <c r="F41" s="68" t="s">
+      <c r="G41" s="68" t="s">
         <v>1354</v>
       </c>
-      <c r="G41" s="68" t="s">
+      <c r="H41" s="68" t="s">
         <v>1355</v>
       </c>
-      <c r="H41" s="68" t="s">
+      <c r="I41" s="68" t="s">
         <v>1356</v>
       </c>
-      <c r="I41" s="68" t="s">
-        <v>1357</v>
-      </c>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="72"/>
+      <c r="A42" s="77"/>
       <c r="B42" s="68">
         <v>2</v>
       </c>
       <c r="C42" s="68" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="D42" s="68">
         <v>3</v>
       </c>
       <c r="E42" s="68" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F42" s="68" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G42" s="68" t="s">
         <v>1359</v>
-      </c>
-      <c r="G42" s="68" t="s">
-        <v>1360</v>
       </c>
       <c r="H42" s="68"/>
       <c r="I42" s="69" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="72"/>
+      <c r="A43" s="77"/>
       <c r="B43" s="68">
         <v>3</v>
       </c>
       <c r="C43" s="68" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="D43" s="68">
         <v>3</v>
       </c>
       <c r="E43" s="68" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F43" s="68" t="s">
+        <v>1362</v>
+      </c>
+      <c r="G43" s="68" t="s">
         <v>1363</v>
-      </c>
-      <c r="G43" s="68" t="s">
-        <v>1364</v>
       </c>
       <c r="H43" s="68"/>
       <c r="I43" s="69" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="73"/>
+      <c r="A44" s="78"/>
       <c r="B44" s="68">
         <v>7</v>
       </c>
       <c r="C44" s="68" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="D44" s="68">
         <v>4</v>
       </c>
       <c r="E44" s="68" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="F44" s="68" t="s">
+        <v>1366</v>
+      </c>
+      <c r="G44" s="68" t="s">
         <v>1367</v>
       </c>
-      <c r="G44" s="68" t="s">
+      <c r="H44" s="68" t="s">
         <v>1368</v>
       </c>
-      <c r="H44" s="68" t="s">
+      <c r="I44" s="68" t="s">
         <v>1369</v>
       </c>
-      <c r="I44" s="68" t="s">
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="76" t="s">
         <v>1370</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" s="71" t="s">
-        <v>1371</v>
       </c>
       <c r="B45" s="68">
         <v>11</v>
       </c>
       <c r="C45" s="68" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="D45" s="68">
         <v>4</v>
       </c>
       <c r="E45" s="68" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F45" s="68" t="s">
         <v>1373</v>
       </c>
-      <c r="F45" s="68" t="s">
+      <c r="G45" s="68" t="s">
         <v>1374</v>
       </c>
-      <c r="G45" s="68" t="s">
+      <c r="H45" s="68" t="s">
         <v>1375</v>
       </c>
-      <c r="H45" s="68" t="s">
+      <c r="I45" s="68" t="s">
         <v>1376</v>
       </c>
-      <c r="I45" s="68" t="s">
-        <v>1377</v>
-      </c>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="72"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="68">
         <v>13</v>
       </c>
       <c r="C46" s="68" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D46" s="68">
         <v>5</v>
       </c>
       <c r="E46" s="68" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="F46" s="68" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G46" s="68" t="s">
         <v>1379</v>
       </c>
-      <c r="G46" s="68" t="s">
+      <c r="H46" s="68" t="s">
         <v>1380</v>
       </c>
-      <c r="H46" s="68" t="s">
+      <c r="I46" s="68" t="s">
         <v>1381</v>
       </c>
-      <c r="I46" s="68" t="s">
-        <v>1382</v>
-      </c>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="72"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="68">
         <v>15</v>
       </c>
       <c r="C47" s="68" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="D47" s="68">
         <v>4</v>
       </c>
       <c r="E47" s="68" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="F47" s="68" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G47" s="68" t="s">
         <v>1384</v>
       </c>
-      <c r="G47" s="68" t="s">
+      <c r="H47" s="68" t="s">
         <v>1385</v>
       </c>
-      <c r="H47" s="68" t="s">
+      <c r="I47" s="68" t="s">
         <v>1386</v>
       </c>
-      <c r="I47" s="68" t="s">
-        <v>1387</v>
-      </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="73"/>
+      <c r="A48" s="78"/>
       <c r="B48" s="68">
         <v>17</v>
       </c>
       <c r="C48" s="68" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="D48" s="68">
         <v>4</v>
       </c>
       <c r="E48" s="68" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="F48" s="68" t="s">
+        <v>1388</v>
+      </c>
+      <c r="G48" s="68" t="s">
         <v>1389</v>
       </c>
-      <c r="G48" s="68" t="s">
+      <c r="H48" s="68" t="s">
         <v>1390</v>
       </c>
-      <c r="H48" s="68" t="s">
+      <c r="I48" s="68" t="s">
         <v>1391</v>
-      </c>
-      <c r="I48" s="68" t="s">
-        <v>1392</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="69" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B51" s="68" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C51" s="68" t="s">
+        <v>1345</v>
+      </c>
+      <c r="D51" s="68" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E51" s="68" t="s">
+        <v>1347</v>
+      </c>
+      <c r="F51" s="68" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G51" s="68" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H51" s="68" t="s">
+        <v>1348</v>
+      </c>
+      <c r="I51" s="68" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="79" t="s">
         <v>1393</v>
-      </c>
-      <c r="B51" s="68" t="s">
-        <v>1345</v>
-      </c>
-      <c r="C51" s="68" t="s">
-        <v>1346</v>
-      </c>
-      <c r="D51" s="68" t="s">
-        <v>1347</v>
-      </c>
-      <c r="E51" s="68" t="s">
-        <v>1348</v>
-      </c>
-      <c r="F51" s="68" t="s">
-        <v>1349</v>
-      </c>
-      <c r="G51" s="68" t="s">
-        <v>1349</v>
-      </c>
-      <c r="H51" s="68" t="s">
-        <v>1349</v>
-      </c>
-      <c r="I51" s="68" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="74" t="s">
-        <v>1394</v>
       </c>
       <c r="B52" s="68">
         <v>1</v>
       </c>
       <c r="C52" s="68" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D52" s="68">
         <v>4</v>
       </c>
       <c r="E52" s="68" t="s">
+        <v>1395</v>
+      </c>
+      <c r="F52" s="68" t="s">
         <v>1396</v>
       </c>
-      <c r="F52" s="68" t="s">
+      <c r="G52" s="68" t="s">
         <v>1397</v>
       </c>
-      <c r="G52" s="68" t="s">
+      <c r="H52" s="68" t="s">
         <v>1398</v>
       </c>
-      <c r="H52" s="68" t="s">
+      <c r="I52" s="70" t="s">
         <v>1399</v>
       </c>
-      <c r="I52" s="70" t="s">
-        <v>1400</v>
-      </c>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="74"/>
+      <c r="A53" s="79"/>
       <c r="B53" s="68">
         <v>4</v>
       </c>
       <c r="C53" s="68" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="D53" s="68">
         <v>5</v>
       </c>
       <c r="E53" s="68" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="F53" s="68" t="s">
+        <v>1401</v>
+      </c>
+      <c r="G53" s="68" t="s">
         <v>1402</v>
       </c>
-      <c r="G53" s="68" t="s">
+      <c r="H53" s="68" t="s">
         <v>1403</v>
       </c>
-      <c r="H53" s="68" t="s">
+      <c r="I53" s="70" t="s">
         <v>1404</v>
       </c>
-      <c r="I53" s="70" t="s">
-        <v>1405</v>
-      </c>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="74"/>
+      <c r="A54" s="79"/>
       <c r="B54" s="68">
         <v>6</v>
       </c>
       <c r="C54" s="68" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="D54" s="68">
         <v>5</v>
       </c>
       <c r="E54" s="68" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="F54" s="68" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G54" s="68" t="s">
         <v>1407</v>
       </c>
-      <c r="G54" s="68" t="s">
+      <c r="H54" s="68" t="s">
         <v>1408</v>
       </c>
-      <c r="H54" s="68" t="s">
+      <c r="I54" s="70" t="s">
         <v>1409</v>
       </c>
-      <c r="I54" s="70" t="s">
-        <v>1410</v>
-      </c>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="74"/>
+      <c r="A55" s="79"/>
       <c r="B55" s="68">
         <v>8</v>
       </c>
       <c r="C55" s="68" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="D55" s="68">
         <v>3</v>
       </c>
       <c r="E55" s="68" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="F55" s="68" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G55" s="68" t="s">
         <v>1412</v>
-      </c>
-      <c r="G55" s="68" t="s">
-        <v>1413</v>
       </c>
       <c r="H55" s="68"/>
       <c r="I55" s="70" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="79" t="s">
         <v>1414</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="74" t="s">
-        <v>1415</v>
       </c>
       <c r="B56" s="68">
         <v>10</v>
       </c>
       <c r="C56" s="68" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="D56" s="68">
         <v>4</v>
       </c>
       <c r="E56" s="68" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F56" s="68" t="s">
         <v>1417</v>
       </c>
-      <c r="F56" s="68" t="s">
+      <c r="G56" s="68" t="s">
         <v>1418</v>
       </c>
-      <c r="G56" s="68" t="s">
+      <c r="H56" s="68" t="s">
         <v>1419</v>
       </c>
-      <c r="H56" s="68" t="s">
+      <c r="I56" s="70" t="s">
         <v>1420</v>
       </c>
-      <c r="I56" s="70" t="s">
-        <v>1421</v>
-      </c>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="74"/>
+      <c r="A57" s="79"/>
       <c r="B57" s="68">
         <v>11</v>
       </c>
       <c r="C57" s="68" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="D57" s="68">
         <v>4</v>
       </c>
       <c r="E57" s="68" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="F57" s="68" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G57" s="68" t="s">
         <v>1423</v>
       </c>
-      <c r="G57" s="68" t="s">
+      <c r="H57" s="68" t="s">
         <v>1424</v>
       </c>
-      <c r="H57" s="68" t="s">
+      <c r="I57" s="70" t="s">
         <v>1425</v>
       </c>
-      <c r="I57" s="70" t="s">
-        <v>1426</v>
-      </c>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="74"/>
+      <c r="A58" s="79"/>
       <c r="B58" s="68">
         <v>12</v>
       </c>
       <c r="C58" s="68" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="D58" s="68">
         <v>4</v>
       </c>
       <c r="E58" s="68" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="F58" s="68" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G58" s="68" t="s">
         <v>1428</v>
       </c>
-      <c r="G58" s="68" t="s">
+      <c r="H58" s="68" t="s">
         <v>1429</v>
       </c>
-      <c r="H58" s="68" t="s">
+      <c r="I58" s="70" t="s">
         <v>1430</v>
       </c>
-      <c r="I58" s="70" t="s">
-        <v>1431</v>
-      </c>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="74"/>
+      <c r="A59" s="79"/>
       <c r="B59" s="68">
         <v>14</v>
       </c>
       <c r="C59" s="68" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="D59" s="68">
         <v>4</v>
       </c>
       <c r="E59" s="68" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="F59" s="68" t="s">
+        <v>1432</v>
+      </c>
+      <c r="G59" s="68" t="s">
         <v>1433</v>
       </c>
-      <c r="G59" s="68" t="s">
+      <c r="H59" s="68" t="s">
         <v>1434</v>
       </c>
-      <c r="H59" s="68" t="s">
+      <c r="I59" s="70" t="s">
         <v>1435</v>
-      </c>
-      <c r="I59" s="70" t="s">
-        <v>1436</v>
       </c>
     </row>
   </sheetData>
@@ -26399,6 +26419,23 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EE14F7-3A2C-2244-AED7-8B110D2B5190}">
+  <dimension ref="B3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="3" spans="2:2">
+      <c r="B3">
+        <f>EXP(3.37)</f>
+        <v>29.078527057797078</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA7C430-7738-A84B-BFA9-AD3645C1BF55}">
   <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
@@ -27778,7 +27815,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08CA6B99-C27B-4F97-B079-228CC4A6ABC1}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
@@ -28382,7 +28419,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5668750C-27A9-4830-BBCD-A49BEBB03C2E}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
@@ -29010,7 +29047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6E27160-7128-40E1-9AE3-BF05BBDBFACD}">
   <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
@@ -29660,63 +29697,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A84558C-36C6-4B03-911F-84558FD8E17A}">
-  <dimension ref="B1:D4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
-  <cols>
-    <col min="3" max="4" width="13.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:4">
-      <c r="B1" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1281</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="2" spans="2:4">
-      <c r="B2">
-        <v>128</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4">
-      <c r="B3">
-        <v>256</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4">
-      <c r="B4">
-        <v>512</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
 </file>